--- a/test_results/Marvin_Test_Log_Luke_2026-10-16.xlsx
+++ b/test_results/Marvin_Test_Log_Luke_2026-10-16.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mygcuedu6961-my.sharepoint.com/personal/rgerhart_my_gcu_edu/Documents/College/CST-440/CST440_programs/CST440AudioML2/test_results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_15CA51F2FE9E7A14DF2961361F77622178DA9477" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3C57854-E934-483D-B015-AF5EDB3C68A7}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="2200" yWindow="2200" windowWidth="17280" windowHeight="9980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Guess Log" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Guess Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Guess Log'!$A$1:$H$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Guess Log'!$A$1:$H$170</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,155 +42,149 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="46">
   <si>
-    <t xml:space="preserve">Word</t>
+    <t>Word</t>
   </si>
   <si>
-    <t xml:space="preserve">Guesses</t>
+    <t>Guesses</t>
   </si>
   <si>
-    <t xml:space="preserve">Correct</t>
+    <t>Correct</t>
   </si>
   <si>
-    <t xml:space="preserve">Accuracy</t>
+    <t>Accuracy</t>
   </si>
   <si>
-    <t xml:space="preserve">Avg confidence (all guesses)</t>
+    <t>Avg confidence (all guesses)</t>
   </si>
   <si>
-    <t xml:space="preserve">Avg confidence (correct only)</t>
+    <t>Avg confidence (correct only)</t>
   </si>
   <si>
-    <t xml:space="preserve">Guesses at 80%+</t>
+    <t>Guesses at 80%+</t>
   </si>
   <si>
-    <t xml:space="preserve">Guesses under 60%</t>
+    <t>Guesses under 60%</t>
   </si>
   <si>
-    <t xml:space="preserve">Avg loudness</t>
+    <t>Avg loudness</t>
   </si>
   <si>
-    <t xml:space="preserve">marvin</t>
+    <t>marvin</t>
   </si>
   <si>
-    <t xml:space="preserve">yes</t>
+    <t>yes</t>
   </si>
   <si>
-    <t xml:space="preserve">no</t>
+    <t>no</t>
   </si>
   <si>
-    <t xml:space="preserve">go</t>
+    <t>go</t>
   </si>
   <si>
-    <t xml:space="preserve">stop</t>
+    <t>stop</t>
   </si>
   <si>
-    <t xml:space="preserve">All words</t>
+    <t>All words</t>
   </si>
   <si>
-    <t xml:space="preserve">Idle (no talking)</t>
+    <t>Idle (no talking)</t>
   </si>
   <si>
-    <t xml:space="preserve">Wake-ups</t>
+    <t>Wake-ups</t>
   </si>
   <si>
-    <t xml:space="preserve">Commands carried out</t>
+    <t>Commands carried out</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes</t>
+    <t>Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: Arduino IDE Serial Monitor log from Luke's Marvin test on 10/16/2026 (Nano 33 BLE, COM5, 115200 baud, debug on).</t>
+    <t>Source: Arduino IDE Serial Monitor log from Luke's Marvin test on 10/16/2026 (Nano 33 BLE, COM5, 115200 baud, debug on).</t>
   </si>
   <si>
-    <t xml:space="preserve">"Word being tested" is the word you were saying at the time. Guesses at a switch between words count toward the next word.</t>
+    <t>"Word being tested" is the word you were saying at the time. Guesses at a switch between words count toward the next word.</t>
   </si>
   <si>
-    <t xml:space="preserve">"Correct only" averages leave out guesses where Marvin picked the wrong word.</t>
+    <t>"Correct only" averages leave out guesses where Marvin picked the wrong word.</t>
   </si>
   <si>
-    <t xml:space="preserve">Commands carried out is 0 because yes/no/go/stop were tested without saying "marvin" first. These rows show accuracy only.</t>
+    <t>Commands carried out is 0 because yes/no/go/stop were tested without saying "marvin" first. These rows show accuracy only.</t>
   </si>
   <si>
-    <t xml:space="preserve">#</t>
+    <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">Debug session</t>
+    <t>Debug session</t>
   </si>
   <si>
-    <t xml:space="preserve">Word being tested</t>
+    <t>Word being tested</t>
   </si>
   <si>
-    <t xml:space="preserve">Marvin heard</t>
+    <t>Marvin heard</t>
   </si>
   <si>
-    <t xml:space="preserve">Confidence</t>
+    <t>Confidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Loudness</t>
+    <t>Loudness</t>
   </si>
   <si>
-    <t xml:space="preserve">Correct?</t>
+    <t>Correct?</t>
   </si>
   <si>
-    <t xml:space="preserve">Note</t>
+    <t>Note</t>
   </si>
   <si>
-    <t xml:space="preserve">idle</t>
+    <t>idle</t>
   </si>
   <si>
-    <t xml:space="preserve">silence</t>
+    <t>silence</t>
   </si>
   <si>
-    <t xml:space="preserve">Woke up: "Heard my name (60%)" at 257.94 s</t>
+    <t>Woke up: "Heard my name (60%)" at 257.94 s</t>
   </si>
   <si>
-    <t xml:space="preserve">No command heard, back to sleep (261.00 s)</t>
+    <t>No command heard, back to sleep (261.00 s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Woke up: "Heard my name (93%)" at 261.77 s</t>
+    <t>Woke up: "Heard my name (93%)" at 261.77 s</t>
   </si>
   <si>
-    <t xml:space="preserve">No command heard, back to sleep (264.83 s)</t>
+    <t>No command heard, back to sleep (264.83 s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Woke up: "Heard my name (80%)" at 265.59 s</t>
+    <t>Woke up: "Heard my name (80%)" at 265.59 s</t>
   </si>
   <si>
-    <t xml:space="preserve">No command heard, back to sleep (268.65 s)</t>
+    <t>No command heard, back to sleep (268.65 s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Woke up: "Heard my name (91%)" at 269.42 s</t>
+    <t>Woke up: "Heard my name (91%)" at 269.42 s</t>
   </si>
   <si>
-    <t xml:space="preserve">No command heard, back to sleep (272.48 s)</t>
+    <t>No command heard, back to sleep (272.48 s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Woke up: "Heard my name (93%)" at 273.25 s</t>
+    <t>Woke up: "Heard my name (93%)" at 273.25 s</t>
   </si>
   <si>
-    <t xml:space="preserve">Not talking here (Luke confirmed)</t>
+    <t>Not talking here (Luke confirmed)</t>
   </si>
   <si>
-    <t xml:space="preserve">No command heard, back to sleep (276.31 s)</t>
+    <t>No command heard, back to sleep (276.31 s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Switching from no to go</t>
+    <t>Switching from no to go</t>
   </si>
   <si>
-    <t xml:space="preserve">Switching from go to stop</t>
+    <t>Switching from go to stop</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
-    <numFmt numFmtId="167" formatCode="0.00"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,47 +193,28 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -241,21 +232,23 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -265,160 +258,53 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF3CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00878F"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD4EDDA"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3CD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D7DA"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -429,11 +315,26 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFD4EDDA"/>
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -492,51 +393,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -544,12 +457,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -578,7 +491,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -599,7 +512,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -650,7 +563,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -668,27 +581,26 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="14"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,229 +629,229 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <f aca="false">COUNTIF('Guess Log'!$C$2:$C$170,A2)</f>
+      <c r="B2" s="3">
+        <f>COUNTIF('Guess Log'!$C$2:$C$170,A2)</f>
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$G$2:$G$170,"Yes")</f>
+      <c r="C2" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$G$2:$G$170,"Yes")</f>
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <f aca="false">IF(B2=0,0,C2/B2)</f>
+      <c r="D2" s="4">
+        <f t="shared" ref="D2:D7" si="0">IF(B2=0,0,C2/B2)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$E$2:$E$170)</f>
-        <v>0.860434782608696</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A2,'Guess Log'!$G$2:$G$170,"Yes")</f>
-        <v>0.860434782608696</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$D$2:$D$170,A2,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
+      <c r="E2" s="4">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$E$2:$E$170)</f>
+        <v>0.86043478260869577</v>
+      </c>
+      <c r="F2" s="4">
+        <f>AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A2,'Guess Log'!$G$2:$G$170,"Yes")</f>
+        <v>0.86043478260869577</v>
+      </c>
+      <c r="G2" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$D$2:$D$170,A2,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
         <v>19</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$D$2:$D$170,A2,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
-        <v>2</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$F$2:$F$170)</f>
-        <v>0.0365217391304348</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$D$2:$D$170,A2,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="5">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A2,'Guess Log'!$F$2:$F$170)</f>
+        <v>3.6521739130434792E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <f aca="false">COUNTIF('Guess Log'!$C$2:$C$170,A3)</f>
+      <c r="B3" s="3">
+        <f>COUNTIF('Guess Log'!$C$2:$C$170,A3)</f>
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$G$2:$G$170,"Yes")</f>
+      <c r="C3" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$G$2:$G$170,"Yes")</f>
         <v>23</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <f aca="false">IF(B3=0,0,C3/B3)</f>
-        <v>0.958333333333333</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$E$2:$E$170)</f>
+      <c r="D3" s="4">
+        <f t="shared" si="0"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E3" s="4">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$E$2:$E$170)</f>
         <v>0.77</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A3,'Guess Log'!$G$2:$G$170,"Yes")</f>
-        <v>0.790434782608696</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$D$2:$D$170,A3,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
+      <c r="F3" s="4">
+        <f>AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A3,'Guess Log'!$G$2:$G$170,"Yes")</f>
+        <v>0.7904347826086956</v>
+      </c>
+      <c r="G3" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$D$2:$D$170,A3,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
         <v>14</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$D$2:$D$170,A3,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
+      <c r="H3" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$D$2:$D$170,A3,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$F$2:$F$170)</f>
-        <v>0.0533333333333333</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I3" s="5">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A3,'Guess Log'!$F$2:$F$170)</f>
+        <v>5.3333333333333365E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <f aca="false">COUNTIF('Guess Log'!$C$2:$C$170,A4)</f>
+      <c r="B4" s="3">
+        <f>COUNTIF('Guess Log'!$C$2:$C$170,A4)</f>
         <v>24</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$G$2:$G$170,"Yes")</f>
+      <c r="C4" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$G$2:$G$170,"Yes")</f>
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <f aca="false">IF(B4=0,0,C4/B4)</f>
-        <v>0.958333333333333</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$E$2:$E$170)</f>
-        <v>0.86625</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A4,'Guess Log'!$G$2:$G$170,"Yes")</f>
-        <v>0.890869565217391</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$D$2:$D$170,A4,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E4" s="4">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$E$2:$E$170)</f>
+        <v>0.86625000000000008</v>
+      </c>
+      <c r="F4" s="4">
+        <f>AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A4,'Guess Log'!$G$2:$G$170,"Yes")</f>
+        <v>0.89086956521739136</v>
+      </c>
+      <c r="G4" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$D$2:$D$170,A4,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
         <v>19</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$D$2:$D$170,A4,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
-        <v>2</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$F$2:$F$170)</f>
-        <v>0.05875</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$D$2:$D$170,A4,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A4,'Guess Log'!$F$2:$F$170)</f>
+        <v>5.8750000000000031E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <f aca="false">COUNTIF('Guess Log'!$C$2:$C$170,A5)</f>
+      <c r="B5" s="3">
+        <f>COUNTIF('Guess Log'!$C$2:$C$170,A5)</f>
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$G$2:$G$170,"Yes")</f>
+      <c r="C5" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$G$2:$G$170,"Yes")</f>
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <f aca="false">IF(B5=0,0,C5/B5)</f>
-        <v>0.962962962962963</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$E$2:$E$170)</f>
-        <v>0.857777777777778</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A5,'Guess Log'!$G$2:$G$170,"Yes")</f>
-        <v>0.881538461538462</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$D$2:$D$170,A5,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
+      <c r="D5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="E5" s="4">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$E$2:$E$170)</f>
+        <v>0.85777777777777775</v>
+      </c>
+      <c r="F5" s="4">
+        <f>AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A5,'Guess Log'!$G$2:$G$170,"Yes")</f>
+        <v>0.88153846153846149</v>
+      </c>
+      <c r="G5" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$D$2:$D$170,A5,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
         <v>22</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$D$2:$D$170,A5,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
-        <v>2</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$F$2:$F$170)</f>
-        <v>0.0655555555555556</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$D$2:$D$170,A5,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A5,'Guess Log'!$F$2:$F$170)</f>
+        <v>6.5555555555555575E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <f aca="false">COUNTIF('Guess Log'!$C$2:$C$170,A6)</f>
+      <c r="B6" s="3">
+        <f>COUNTIF('Guess Log'!$C$2:$C$170,A6)</f>
         <v>42</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$G$2:$G$170,"Yes")</f>
+      <c r="C6" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$G$2:$G$170,"Yes")</f>
         <v>40</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <f aca="false">IF(B6=0,0,C6/B6)</f>
-        <v>0.952380952380952</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$E$2:$E$170)</f>
-        <v>0.725238095238095</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A6,'Guess Log'!$G$2:$G$170,"Yes")</f>
-        <v>0.73825</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$D$2:$D$170,A6,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="E6" s="4">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$E$2:$E$170)</f>
+        <v>0.72523809523809546</v>
+      </c>
+      <c r="F6" s="4">
+        <f>AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,A6,'Guess Log'!$G$2:$G$170,"Yes")</f>
+        <v>0.73825000000000018</v>
+      </c>
+      <c r="G6" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$D$2:$D$170,A6,'Guess Log'!$E$2:$E$170,"&gt;=0.8")</f>
         <v>18</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <f aca="false">COUNTIFS('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$D$2:$D$170,A6,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
-        <v>13</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$F$2:$F$170)</f>
-        <v>0.0602380952380952</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="3">
+        <f>COUNTIFS('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$D$2:$D$170,A6,'Guess Log'!$E$2:$E$170,"&lt;0.6")</f>
+        <v>13</v>
+      </c>
+      <c r="I6" s="5">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,A6,'Guess Log'!$F$2:$F$170)</f>
+        <v>6.0238095238095243E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="n">
-        <f aca="false">SUM(B2:B6)</f>
+      <c r="B7" s="7">
+        <f>SUM(B2:B6)</f>
         <v>140</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <f aca="false">SUM(C2:C6)</f>
+      <c r="C7" s="7">
+        <f>SUM(C2:C6)</f>
         <v>135</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <f aca="false">IF(B7=0,0,C7/B7)</f>
-        <v>0.964285714285714</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,"&lt;&gt;idle")</f>
-        <v>0.804857142857143</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$G$2:$G$170,"Yes")</f>
-        <v>0.821555555555556</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <f aca="false">SUM(G2:G6)</f>
+      <c r="D7" s="8">
+        <f t="shared" si="0"/>
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$C$2:$C$170,"&lt;&gt;idle")</f>
+        <v>0.80485714285714305</v>
+      </c>
+      <c r="F7" s="8">
+        <f>AVERAGEIFS('Guess Log'!$E$2:$E$170,'Guess Log'!$G$2:$G$170,"Yes")</f>
+        <v>0.82155555555555559</v>
+      </c>
+      <c r="G7" s="7">
+        <f>SUM(G2:G6)</f>
         <v>92</v>
       </c>
-      <c r="H7" s="7" t="n">
-        <f aca="false">SUM(H2:H6)</f>
+      <c r="H7" s="7">
+        <f>SUM(H2:H6)</f>
         <v>24</v>
       </c>
-      <c r="I7" s="9" t="n">
-        <f aca="false">AVERAGEIFS('Guess Log'!$F$2:$F$170,'Guess Log'!$C$2:$C$170,"&lt;&gt;idle")</f>
-        <v>0.0559285714285714</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I7" s="9">
+        <f>AVERAGEIFS('Guess Log'!$F$2:$F$170,'Guess Log'!$C$2:$C$170,"&lt;&gt;idle")</f>
+        <v>5.5928571428571397E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -950,29 +862,29 @@
       <c r="H8" s="3"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="n">
-        <f aca="false">COUNTIF('Guess Log'!$C$2:$C$170,"idle")</f>
+      <c r="B9" s="3">
+        <f>COUNTIF('Guess Log'!$C$2:$C$170,"idle")</f>
         <v>29</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="4" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,"idle",'Guess Log'!$E$2:$E$170)</f>
-        <v>0.266551724137931</v>
+      <c r="E9" s="4">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,"idle",'Guess Log'!$E$2:$E$170)</f>
+        <v>0.26655172413793099</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="5" t="n">
-        <f aca="false">AVERAGEIF('Guess Log'!$C$2:$C$170,"idle",'Guess Log'!$F$2:$F$170)</f>
-        <v>0.0210344827586207</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="5">
+        <f>AVERAGEIF('Guess Log'!$C$2:$C$170,"idle",'Guess Log'!$F$2:$F$170)</f>
+        <v>2.1034482758620698E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -983,12 +895,12 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <f aca="false">COUNTIF('Guess Log'!$H$2:$H$170,"Woke up*")</f>
+      <c r="B11" s="3">
+        <f>COUNTIF('Guess Log'!$H$2:$H$170,"Woke up*")</f>
         <v>5</v>
       </c>
       <c r="C11" s="2"/>
@@ -999,11 +911,11 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="10">
         <v>0</v>
       </c>
       <c r="C12" s="2"/>
@@ -1014,7 +926,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1025,7 +937,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A14" s="11" t="s">
         <v>18</v>
       </c>
@@ -1038,7 +950,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -1051,7 +963,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
@@ -1064,7 +976,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
@@ -1077,7 +989,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
@@ -1092,38 +1004,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E6">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H170"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="46"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" ht="27.35" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1149,11 +1053,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -1162,23 +1066,23 @@
       <c r="D2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="13" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F2" s="14" t="n">
+      <c r="E2" s="13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F2" s="14">
         <v>0.02</v>
       </c>
       <c r="G2" s="12" t="str">
-        <f aca="false">IF(C2="idle","n/a",IF(C2=D2,"Yes","No"))</f>
+        <f>IF(C2="idle","n/a",IF(C2=D2,"Yes","No"))</f>
         <v>n/a</v>
       </c>
       <c r="H2" s="15"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -1187,23 +1091,23 @@
       <c r="D3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="13">
         <v>0.26</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="14">
         <v>0.02</v>
       </c>
       <c r="G3" s="12" t="str">
-        <f aca="false">IF(C3="idle","n/a",IF(C3=D3,"Yes","No"))</f>
+        <f t="shared" ref="G2:G33" si="0">IF(C3="idle","n/a",IF(C3=D3,"Yes","No"))</f>
         <v>n/a</v>
       </c>
       <c r="H3" s="15"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -1212,23 +1116,23 @@
       <c r="D4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="13">
         <v>0.3</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="14">
         <v>0.02</v>
       </c>
       <c r="G4" s="12" t="str">
-        <f aca="false">IF(C4="idle","n/a",IF(C4=D4,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="12" t="s">
@@ -1237,23 +1141,23 @@
       <c r="D5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="13">
         <v>0.26</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="14">
         <v>0.02</v>
       </c>
       <c r="G5" s="12" t="str">
-        <f aca="false">IF(C5="idle","n/a",IF(C5=D5,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H5" s="15"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -1262,23 +1166,23 @@
       <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="13">
         <v>0.26</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="14">
         <v>0.02</v>
       </c>
       <c r="G6" s="12" t="str">
-        <f aca="false">IF(C6="idle","n/a",IF(C6=D6,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -1287,23 +1191,23 @@
       <c r="D7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="13">
         <v>0.26</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="14">
         <v>0.02</v>
       </c>
       <c r="G7" s="12" t="str">
-        <f aca="false">IF(C7="idle","n/a",IF(C7=D7,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -1312,23 +1216,23 @@
       <c r="D8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="13">
         <v>0.3</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="14">
         <v>0.02</v>
       </c>
       <c r="G8" s="12" t="str">
-        <f aca="false">IF(C8="idle","n/a",IF(C8=D8,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
@@ -1337,23 +1241,23 @@
       <c r="D9" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="13">
         <v>0.26</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="14">
         <v>0.02</v>
       </c>
       <c r="G9" s="12" t="str">
-        <f aca="false">IF(C9="idle","n/a",IF(C9=D9,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H9" s="15"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A10" s="12">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12">
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -1362,23 +1266,23 @@
       <c r="D10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="13">
         <v>0.25</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="14">
         <v>0.02</v>
       </c>
       <c r="G10" s="12" t="str">
-        <f aca="false">IF(C10="idle","n/a",IF(C10=D10,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="12">
         <v>1</v>
       </c>
       <c r="C11" s="12" t="s">
@@ -1387,23 +1291,23 @@
       <c r="D11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="13">
         <v>0.23</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="14">
         <v>0.02</v>
       </c>
       <c r="G11" s="12" t="str">
-        <f aca="false">IF(C11="idle","n/a",IF(C11=D11,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H11" s="15"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="12">
         <v>1</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -1412,23 +1316,23 @@
       <c r="D12" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="13" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F12" s="14" t="n">
+      <c r="E12" s="13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F12" s="14">
         <v>0.02</v>
       </c>
       <c r="G12" s="12" t="str">
-        <f aca="false">IF(C12="idle","n/a",IF(C12=D12,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H12" s="15"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A13" s="12">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12">
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -1437,23 +1341,23 @@
       <c r="D13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="13">
         <v>0.23</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="14">
         <v>0.02</v>
       </c>
       <c r="G13" s="12" t="str">
-        <f aca="false">IF(C13="idle","n/a",IF(C13=D13,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A14" s="12">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12">
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
@@ -1462,23 +1366,23 @@
       <c r="D14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="13">
         <v>0.32</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="14">
         <v>0.02</v>
       </c>
       <c r="G14" s="12" t="str">
-        <f aca="false">IF(C14="idle","n/a",IF(C14=D14,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="12">
         <v>1</v>
       </c>
       <c r="C15" s="12" t="s">
@@ -1487,23 +1391,23 @@
       <c r="D15" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="13">
         <v>0.27</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="14">
         <v>0.01</v>
       </c>
       <c r="G15" s="12" t="str">
-        <f aca="false">IF(C15="idle","n/a",IF(C15=D15,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="12">
         <v>1</v>
       </c>
       <c r="C16" s="12" t="s">
@@ -1512,23 +1416,23 @@
       <c r="D16" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="13">
         <v>0.25</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="14">
         <v>0.01</v>
       </c>
       <c r="G16" s="12" t="str">
-        <f aca="false">IF(C16="idle","n/a",IF(C16=D16,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="n">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="12">
         <v>1</v>
       </c>
       <c r="C17" s="12" t="s">
@@ -1537,23 +1441,23 @@
       <c r="D17" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="13">
         <v>0.25</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="14">
         <v>0.02</v>
       </c>
       <c r="G17" s="12" t="str">
-        <f aca="false">IF(C17="idle","n/a",IF(C17=D17,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H17" s="15"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="n">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="12">
         <v>1</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -1562,23 +1466,23 @@
       <c r="D18" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="13">
         <v>0.26</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="14">
         <v>0.02</v>
       </c>
       <c r="G18" s="12" t="str">
-        <f aca="false">IF(C18="idle","n/a",IF(C18=D18,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H18" s="15"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="n">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="12">
         <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -1587,23 +1491,23 @@
       <c r="D19" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="13">
         <v>0.26</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="14">
         <v>0.02</v>
       </c>
       <c r="G19" s="12" t="str">
-        <f aca="false">IF(C19="idle","n/a",IF(C19=D19,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H19" s="15"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="n">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="12">
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -1612,23 +1516,23 @@
       <c r="D20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="13" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F20" s="14" t="n">
+      <c r="E20" s="13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F20" s="14">
         <v>0.02</v>
       </c>
       <c r="G20" s="12" t="str">
-        <f aca="false">IF(C20="idle","n/a",IF(C20=D20,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="n">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="12">
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
@@ -1637,23 +1541,23 @@
       <c r="D21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="13">
         <v>0.26</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="14">
         <v>0.02</v>
       </c>
       <c r="G21" s="12" t="str">
-        <f aca="false">IF(C21="idle","n/a",IF(C21=D21,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H21" s="15"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="n">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A22" s="12">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="12">
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -1662,23 +1566,23 @@
       <c r="D22" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="13">
         <v>0.25</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="14">
         <v>0.01</v>
       </c>
       <c r="G22" s="12" t="str">
-        <f aca="false">IF(C22="idle","n/a",IF(C22=D22,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H22" s="15"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="n">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A23" s="12">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="12">
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -1687,23 +1591,23 @@
       <c r="D23" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="13">
         <v>0.26</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="F23" s="14">
         <v>0.02</v>
       </c>
       <c r="G23" s="12" t="str">
-        <f aca="false">IF(C23="idle","n/a",IF(C23=D23,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H23" s="15"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="n">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A24" s="12">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="12">
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
@@ -1712,23 +1616,23 @@
       <c r="D24" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="13">
         <v>0.26</v>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="F24" s="14">
         <v>0.02</v>
       </c>
       <c r="G24" s="12" t="str">
-        <f aca="false">IF(C24="idle","n/a",IF(C24=D24,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="n">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A25" s="12">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="12">
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
@@ -1737,23 +1641,23 @@
       <c r="D25" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="13">
         <v>0.23</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="14">
         <v>0.02</v>
       </c>
       <c r="G25" s="12" t="str">
-        <f aca="false">IF(C25="idle","n/a",IF(C25=D25,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H25" s="15"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="n">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A26" s="12">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="12">
         <v>1</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -1762,23 +1666,23 @@
       <c r="D26" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="13">
         <v>0.25</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="14">
         <v>0.02</v>
       </c>
       <c r="G26" s="12" t="str">
-        <f aca="false">IF(C26="idle","n/a",IF(C26=D26,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H26" s="15"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="n">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A27" s="12">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="12">
         <v>1</v>
       </c>
       <c r="C27" s="12" t="s">
@@ -1787,23 +1691,23 @@
       <c r="D27" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="13">
         <v>0.26</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="14">
         <v>0.02</v>
       </c>
       <c r="G27" s="12" t="str">
-        <f aca="false">IF(C27="idle","n/a",IF(C27=D27,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H27" s="15"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="n">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="12">
         <v>2</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -1812,23 +1716,23 @@
       <c r="D28" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="13">
         <v>0.31</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="14">
         <v>0.05</v>
       </c>
       <c r="G28" s="12" t="str">
-        <f aca="false">IF(C28="idle","n/a",IF(C28=D28,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="n">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="12">
         <v>2</v>
       </c>
       <c r="C29" s="12" t="s">
@@ -1837,23 +1741,23 @@
       <c r="D29" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="13" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F29" s="14" t="n">
+      <c r="E29" s="13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F29" s="14">
         <v>0.02</v>
       </c>
       <c r="G29" s="12" t="str">
-        <f aca="false">IF(C29="idle","n/a",IF(C29=D29,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>n/a</v>
       </c>
       <c r="H29" s="15"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="n">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A30" s="12">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="12">
         <v>2</v>
       </c>
       <c r="C30" s="12" t="s">
@@ -1862,25 +1766,25 @@
       <c r="D30" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="13">
         <v>0.91</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="14">
         <v>0.04</v>
       </c>
       <c r="G30" s="12" t="str">
-        <f aca="false">IF(C30="idle","n/a",IF(C30=D30,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="n">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A31" s="12">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="12">
         <v>2</v>
       </c>
       <c r="C31" s="12" t="s">
@@ -1889,23 +1793,23 @@
       <c r="D31" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="13">
         <v>0.94</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="14">
         <v>0.04</v>
       </c>
       <c r="G31" s="12" t="str">
-        <f aca="false">IF(C31="idle","n/a",IF(C31=D31,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
       <c r="H31" s="15"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="n">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="12">
         <v>2</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -1914,23 +1818,23 @@
       <c r="D32" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="13">
         <v>0.96</v>
       </c>
-      <c r="F32" s="14" t="n">
+      <c r="F32" s="14">
         <v>0.03</v>
       </c>
       <c r="G32" s="12" t="str">
-        <f aca="false">IF(C32="idle","n/a",IF(C32=D32,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
       <c r="H32" s="15"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="n">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A33" s="12">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="12">
         <v>2</v>
       </c>
       <c r="C33" s="12" t="s">
@@ -1939,23 +1843,23 @@
       <c r="D33" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="13">
         <v>0.96</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="14">
         <v>0.04</v>
       </c>
       <c r="G33" s="12" t="str">
-        <f aca="false">IF(C33="idle","n/a",IF(C33=D33,"Yes","No"))</f>
+        <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
       <c r="H33" s="15"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="n">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A34" s="12">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="12">
         <v>2</v>
       </c>
       <c r="C34" s="12" t="s">
@@ -1964,25 +1868,25 @@
       <c r="D34" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="13">
         <v>0.91</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="14">
         <v>0.03</v>
       </c>
       <c r="G34" s="12" t="str">
-        <f aca="false">IF(C34="idle","n/a",IF(C34=D34,"Yes","No"))</f>
+        <f t="shared" ref="G34:G65" si="1">IF(C34="idle","n/a",IF(C34=D34,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="n">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A35" s="12">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="12">
         <v>2</v>
       </c>
       <c r="C35" s="12" t="s">
@@ -1991,25 +1895,25 @@
       <c r="D35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="13">
         <v>0.95</v>
       </c>
-      <c r="F35" s="14" t="n">
+      <c r="F35" s="14">
         <v>0.04</v>
       </c>
       <c r="G35" s="12" t="str">
-        <f aca="false">IF(C35="idle","n/a",IF(C35=D35,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="n">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A36" s="12">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="12">
         <v>2</v>
       </c>
       <c r="C36" s="12" t="s">
@@ -2018,23 +1922,23 @@
       <c r="D36" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="13">
         <v>0.94</v>
       </c>
-      <c r="F36" s="14" t="n">
+      <c r="F36" s="14">
         <v>0.04</v>
       </c>
       <c r="G36" s="12" t="str">
-        <f aca="false">IF(C36="idle","n/a",IF(C36=D36,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H36" s="15"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="n">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A37" s="12">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="12">
         <v>2</v>
       </c>
       <c r="C37" s="12" t="s">
@@ -2043,23 +1947,23 @@
       <c r="D37" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="13">
         <v>0.97</v>
       </c>
-      <c r="F37" s="14" t="n">
+      <c r="F37" s="14">
         <v>0.04</v>
       </c>
       <c r="G37" s="12" t="str">
-        <f aca="false">IF(C37="idle","n/a",IF(C37=D37,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H37" s="15"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="n">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A38" s="12">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="12">
         <v>2</v>
       </c>
       <c r="C38" s="12" t="s">
@@ -2068,23 +1972,23 @@
       <c r="D38" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="13">
         <v>0.82</v>
       </c>
-      <c r="F38" s="14" t="n">
+      <c r="F38" s="14">
         <v>0.03</v>
       </c>
       <c r="G38" s="12" t="str">
-        <f aca="false">IF(C38="idle","n/a",IF(C38=D38,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H38" s="15"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="n">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A39" s="12">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="12">
         <v>2</v>
       </c>
       <c r="C39" s="12" t="s">
@@ -2093,25 +1997,25 @@
       <c r="D39" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="13">
         <v>0.85</v>
       </c>
-      <c r="F39" s="14" t="n">
+      <c r="F39" s="14">
         <v>0.04</v>
       </c>
       <c r="G39" s="12" t="str">
-        <f aca="false">IF(C39="idle","n/a",IF(C39=D39,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H39" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="n">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A40" s="12">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="12">
         <v>2</v>
       </c>
       <c r="C40" s="12" t="s">
@@ -2120,25 +2024,25 @@
       <c r="D40" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="13">
         <v>0.75</v>
       </c>
-      <c r="F40" s="14" t="n">
+      <c r="F40" s="14">
         <v>0.04</v>
       </c>
       <c r="G40" s="12" t="str">
-        <f aca="false">IF(C40="idle","n/a",IF(C40=D40,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H40" s="15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="n">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A41" s="12">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="12">
         <v>2</v>
       </c>
       <c r="C41" s="12" t="s">
@@ -2147,23 +2051,23 @@
       <c r="D41" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="13">
         <v>0.82</v>
       </c>
-      <c r="F41" s="14" t="n">
+      <c r="F41" s="14">
         <v>0.03</v>
       </c>
       <c r="G41" s="12" t="str">
-        <f aca="false">IF(C41="idle","n/a",IF(C41=D41,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H41" s="15"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="n">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A42" s="12">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="12">
         <v>2</v>
       </c>
       <c r="C42" s="12" t="s">
@@ -2172,23 +2076,23 @@
       <c r="D42" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="13">
         <v>0.89</v>
       </c>
-      <c r="F42" s="14" t="n">
+      <c r="F42" s="14">
         <v>0.05</v>
       </c>
       <c r="G42" s="12" t="str">
-        <f aca="false">IF(C42="idle","n/a",IF(C42=D42,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H42" s="15"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12" t="n">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A43" s="12">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="12">
         <v>2</v>
       </c>
       <c r="C43" s="12" t="s">
@@ -2197,23 +2101,23 @@
       <c r="D43" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="13">
         <v>0.96</v>
       </c>
-      <c r="F43" s="14" t="n">
+      <c r="F43" s="14">
         <v>0.04</v>
       </c>
       <c r="G43" s="12" t="str">
-        <f aca="false">IF(C43="idle","n/a",IF(C43=D43,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H43" s="15"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12" t="n">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A44" s="12">
         <v>43</v>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="12">
         <v>2</v>
       </c>
       <c r="C44" s="12" t="s">
@@ -2222,25 +2126,25 @@
       <c r="D44" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="13">
         <v>0.97</v>
       </c>
-      <c r="F44" s="14" t="n">
+      <c r="F44" s="14">
         <v>0.04</v>
       </c>
       <c r="G44" s="12" t="str">
-        <f aca="false">IF(C44="idle","n/a",IF(C44=D44,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12" t="n">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A45" s="12">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="12">
         <v>2</v>
       </c>
       <c r="C45" s="12" t="s">
@@ -2249,25 +2153,25 @@
       <c r="D45" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="13">
         <v>0.85</v>
       </c>
-      <c r="F45" s="14" t="n">
+      <c r="F45" s="14">
         <v>0.04</v>
       </c>
       <c r="G45" s="12" t="str">
-        <f aca="false">IF(C45="idle","n/a",IF(C45=D45,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12" t="n">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A46" s="12">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="12">
         <v>2</v>
       </c>
       <c r="C46" s="12" t="s">
@@ -2276,23 +2180,23 @@
       <c r="D46" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="13">
         <v>0.97</v>
       </c>
-      <c r="F46" s="14" t="n">
+      <c r="F46" s="14">
         <v>0.05</v>
       </c>
       <c r="G46" s="12" t="str">
-        <f aca="false">IF(C46="idle","n/a",IF(C46=D46,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H46" s="15"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="n">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A47" s="12">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="12">
         <v>2</v>
       </c>
       <c r="C47" s="12" t="s">
@@ -2301,23 +2205,23 @@
       <c r="D47" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="13">
         <v>0.95</v>
       </c>
-      <c r="F47" s="14" t="n">
+      <c r="F47" s="14">
         <v>0.03</v>
       </c>
       <c r="G47" s="12" t="str">
-        <f aca="false">IF(C47="idle","n/a",IF(C47=D47,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H47" s="15"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="n">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A48" s="12">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="12">
         <v>2</v>
       </c>
       <c r="C48" s="12" t="s">
@@ -2326,23 +2230,23 @@
       <c r="D48" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="13">
         <v>0.74</v>
       </c>
-      <c r="F48" s="14" t="n">
+      <c r="F48" s="14">
         <v>0.03</v>
       </c>
       <c r="G48" s="12" t="str">
-        <f aca="false">IF(C48="idle","n/a",IF(C48=D48,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H48" s="15"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12" t="n">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A49" s="12">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="12">
         <v>2</v>
       </c>
       <c r="C49" s="12" t="s">
@@ -2351,25 +2255,25 @@
       <c r="D49" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="13">
         <v>0.89</v>
       </c>
-      <c r="F49" s="14" t="n">
+      <c r="F49" s="14">
         <v>0.04</v>
       </c>
       <c r="G49" s="12" t="str">
-        <f aca="false">IF(C49="idle","n/a",IF(C49=D49,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H49" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12" t="n">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A50" s="12">
         <v>49</v>
       </c>
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="12">
         <v>2</v>
       </c>
       <c r="C50" s="12" t="s">
@@ -2378,25 +2282,25 @@
       <c r="D50" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="13">
         <v>0.96</v>
       </c>
-      <c r="F50" s="14" t="n">
+      <c r="F50" s="14">
         <v>0.04</v>
       </c>
       <c r="G50" s="12" t="str">
-        <f aca="false">IF(C50="idle","n/a",IF(C50=D50,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H50" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12" t="n">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A51" s="12">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="12">
         <v>2</v>
       </c>
       <c r="C51" s="12" t="s">
@@ -2405,23 +2309,23 @@
       <c r="D51" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F51" s="14" t="n">
+      <c r="E51" s="13">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F51" s="14">
         <v>0.02</v>
       </c>
       <c r="G51" s="12" t="str">
-        <f aca="false">IF(C51="idle","n/a",IF(C51=D51,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H51" s="15"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="n">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A52" s="12">
         <v>51</v>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="12">
         <v>2</v>
       </c>
       <c r="C52" s="12" t="s">
@@ -2430,23 +2334,23 @@
       <c r="D52" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="13">
         <v>0.26</v>
       </c>
-      <c r="F52" s="14" t="n">
+      <c r="F52" s="14">
         <v>0.02</v>
       </c>
       <c r="G52" s="12" t="str">
-        <f aca="false">IF(C52="idle","n/a",IF(C52=D52,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H52" s="15"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12" t="n">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A53" s="12">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="12">
         <v>2</v>
       </c>
       <c r="C53" s="12" t="s">
@@ -2455,25 +2359,25 @@
       <c r="D53" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="13">
         <v>0.27</v>
       </c>
-      <c r="F53" s="14" t="n">
+      <c r="F53" s="14">
         <v>0.05</v>
       </c>
       <c r="G53" s="12" t="str">
-        <f aca="false">IF(C53="idle","n/a",IF(C53=D53,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>n/a</v>
       </c>
       <c r="H53" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12" t="n">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A54" s="12">
         <v>53</v>
       </c>
-      <c r="B54" s="12" t="n">
+      <c r="B54" s="12">
         <v>2</v>
       </c>
       <c r="C54" s="12" t="s">
@@ -2482,25 +2386,25 @@
       <c r="D54" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="13" t="n">
+      <c r="E54" s="13">
         <v>0.98</v>
       </c>
-      <c r="F54" s="14" t="n">
+      <c r="F54" s="14">
         <v>0.06</v>
       </c>
       <c r="G54" s="12" t="str">
-        <f aca="false">IF(C54="idle","n/a",IF(C54=D54,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H54" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="n">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A55" s="12">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="12">
         <v>2</v>
       </c>
       <c r="C55" s="12" t="s">
@@ -2509,23 +2413,23 @@
       <c r="D55" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="13" t="n">
+      <c r="E55" s="13">
         <v>0.88</v>
       </c>
-      <c r="F55" s="14" t="n">
+      <c r="F55" s="14">
         <v>0.06</v>
       </c>
       <c r="G55" s="12" t="str">
-        <f aca="false">IF(C55="idle","n/a",IF(C55=D55,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H55" s="15"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12" t="n">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A56" s="12">
         <v>55</v>
       </c>
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="12">
         <v>2</v>
       </c>
       <c r="C56" s="12" t="s">
@@ -2534,23 +2438,23 @@
       <c r="D56" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="13" t="n">
+      <c r="E56" s="13">
         <v>0.95</v>
       </c>
-      <c r="F56" s="14" t="n">
+      <c r="F56" s="14">
         <v>0.06</v>
       </c>
       <c r="G56" s="12" t="str">
-        <f aca="false">IF(C56="idle","n/a",IF(C56=D56,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H56" s="15"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12" t="n">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A57" s="12">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="12">
         <v>2</v>
       </c>
       <c r="C57" s="12" t="s">
@@ -2559,23 +2463,23 @@
       <c r="D57" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E57" s="13">
         <v>0.93</v>
       </c>
-      <c r="F57" s="14" t="n">
+      <c r="F57" s="14">
         <v>0.05</v>
       </c>
       <c r="G57" s="12" t="str">
-        <f aca="false">IF(C57="idle","n/a",IF(C57=D57,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H57" s="15"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12" t="n">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A58" s="12">
         <v>57</v>
       </c>
-      <c r="B58" s="12" t="n">
+      <c r="B58" s="12">
         <v>2</v>
       </c>
       <c r="C58" s="12" t="s">
@@ -2584,23 +2488,23 @@
       <c r="D58" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="13" t="n">
+      <c r="E58" s="13">
         <v>0.92</v>
       </c>
-      <c r="F58" s="14" t="n">
-        <v>0.07</v>
+      <c r="F58" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G58" s="12" t="str">
-        <f aca="false">IF(C58="idle","n/a",IF(C58=D58,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H58" s="15"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="n">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A59" s="12">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="n">
+      <c r="B59" s="12">
         <v>2</v>
       </c>
       <c r="C59" s="12" t="s">
@@ -2609,23 +2513,23 @@
       <c r="D59" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E59" s="13">
         <v>0.83</v>
       </c>
-      <c r="F59" s="14" t="n">
+      <c r="F59" s="14">
         <v>0.04</v>
       </c>
       <c r="G59" s="12" t="str">
-        <f aca="false">IF(C59="idle","n/a",IF(C59=D59,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H59" s="15"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="n">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A60" s="12">
         <v>59</v>
       </c>
-      <c r="B60" s="12" t="n">
+      <c r="B60" s="12">
         <v>2</v>
       </c>
       <c r="C60" s="12" t="s">
@@ -2634,23 +2538,23 @@
       <c r="D60" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="13" t="n">
+      <c r="E60" s="13">
         <v>0.87</v>
       </c>
-      <c r="F60" s="14" t="n">
+      <c r="F60" s="14">
         <v>0.06</v>
       </c>
       <c r="G60" s="12" t="str">
-        <f aca="false">IF(C60="idle","n/a",IF(C60=D60,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H60" s="15"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="n">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A61" s="12">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="n">
+      <c r="B61" s="12">
         <v>2</v>
       </c>
       <c r="C61" s="12" t="s">
@@ -2659,23 +2563,23 @@
       <c r="D61" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="13" t="n">
+      <c r="E61" s="13">
         <v>0.98</v>
       </c>
-      <c r="F61" s="14" t="n">
+      <c r="F61" s="14">
         <v>0.06</v>
       </c>
       <c r="G61" s="12" t="str">
-        <f aca="false">IF(C61="idle","n/a",IF(C61=D61,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H61" s="15"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12" t="n">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A62" s="12">
         <v>61</v>
       </c>
-      <c r="B62" s="12" t="n">
+      <c r="B62" s="12">
         <v>2</v>
       </c>
       <c r="C62" s="12" t="s">
@@ -2684,23 +2588,23 @@
       <c r="D62" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="13" t="n">
+      <c r="E62" s="13">
         <v>0.79</v>
       </c>
-      <c r="F62" s="14" t="n">
+      <c r="F62" s="14">
         <v>0.05</v>
       </c>
       <c r="G62" s="12" t="str">
-        <f aca="false">IF(C62="idle","n/a",IF(C62=D62,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H62" s="15"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12" t="n">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A63" s="12">
         <v>62</v>
       </c>
-      <c r="B63" s="12" t="n">
+      <c r="B63" s="12">
         <v>2</v>
       </c>
       <c r="C63" s="12" t="s">
@@ -2709,23 +2613,23 @@
       <c r="D63" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="13">
         <v>0.8</v>
       </c>
-      <c r="F63" s="14" t="n">
-        <v>0.07</v>
+      <c r="F63" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G63" s="12" t="str">
-        <f aca="false">IF(C63="idle","n/a",IF(C63=D63,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H63" s="15"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12" t="n">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A64" s="12">
         <v>63</v>
       </c>
-      <c r="B64" s="12" t="n">
+      <c r="B64" s="12">
         <v>2</v>
       </c>
       <c r="C64" s="12" t="s">
@@ -2734,23 +2638,23 @@
       <c r="D64" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="13" t="n">
+      <c r="E64" s="13">
         <v>0.3</v>
       </c>
-      <c r="F64" s="14" t="n">
+      <c r="F64" s="14">
         <v>0.06</v>
       </c>
       <c r="G64" s="12" t="str">
-        <f aca="false">IF(C64="idle","n/a",IF(C64=D64,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="H64" s="15"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12" t="n">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A65" s="12">
         <v>64</v>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="12">
         <v>2</v>
       </c>
       <c r="C65" s="12" t="s">
@@ -2759,23 +2663,23 @@
       <c r="D65" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F65" s="14" t="n">
+      <c r="E65" s="13">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F65" s="14">
         <v>0.02</v>
       </c>
       <c r="G65" s="12" t="str">
-        <f aca="false">IF(C65="idle","n/a",IF(C65=D65,"Yes","No"))</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="H65" s="15"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12" t="n">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A66" s="12">
         <v>65</v>
       </c>
-      <c r="B66" s="12" t="n">
+      <c r="B66" s="12">
         <v>2</v>
       </c>
       <c r="C66" s="12" t="s">
@@ -2784,23 +2688,23 @@
       <c r="D66" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="13" t="n">
+      <c r="E66" s="13">
         <v>0.96</v>
       </c>
-      <c r="F66" s="14" t="n">
+      <c r="F66" s="14">
         <v>0.05</v>
       </c>
       <c r="G66" s="12" t="str">
-        <f aca="false">IF(C66="idle","n/a",IF(C66=D66,"Yes","No"))</f>
+        <f t="shared" ref="G66:G97" si="2">IF(C66="idle","n/a",IF(C66=D66,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="H66" s="15"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="n">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A67" s="12">
         <v>66</v>
       </c>
-      <c r="B67" s="12" t="n">
+      <c r="B67" s="12">
         <v>2</v>
       </c>
       <c r="C67" s="12" t="s">
@@ -2809,23 +2713,23 @@
       <c r="D67" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="13">
         <v>0.59</v>
       </c>
-      <c r="F67" s="14" t="n">
-        <v>0.07</v>
+      <c r="F67" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G67" s="12" t="str">
-        <f aca="false">IF(C67="idle","n/a",IF(C67=D67,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H67" s="15"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="n">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A68" s="12">
         <v>67</v>
       </c>
-      <c r="B68" s="12" t="n">
+      <c r="B68" s="12">
         <v>2</v>
       </c>
       <c r="C68" s="12" t="s">
@@ -2834,23 +2738,23 @@
       <c r="D68" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E68" s="13" t="n">
+      <c r="E68" s="13">
         <v>0.89</v>
       </c>
-      <c r="F68" s="14" t="n">
-        <v>0.07</v>
+      <c r="F68" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G68" s="12" t="str">
-        <f aca="false">IF(C68="idle","n/a",IF(C68=D68,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H68" s="15"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="n">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A69" s="12">
         <v>68</v>
       </c>
-      <c r="B69" s="12" t="n">
+      <c r="B69" s="12">
         <v>2</v>
       </c>
       <c r="C69" s="12" t="s">
@@ -2859,23 +2763,23 @@
       <c r="D69" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E69" s="13" t="n">
+      <c r="E69" s="13">
         <v>0.46</v>
       </c>
-      <c r="F69" s="14" t="n">
-        <v>0.07</v>
+      <c r="F69" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G69" s="12" t="str">
-        <f aca="false">IF(C69="idle","n/a",IF(C69=D69,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H69" s="15"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="n">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A70" s="12">
         <v>69</v>
       </c>
-      <c r="B70" s="12" t="n">
+      <c r="B70" s="12">
         <v>2</v>
       </c>
       <c r="C70" s="12" t="s">
@@ -2884,23 +2788,23 @@
       <c r="D70" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="13" t="n">
+      <c r="E70" s="13">
         <v>0.71</v>
       </c>
-      <c r="F70" s="14" t="n">
+      <c r="F70" s="14">
         <v>0.04</v>
       </c>
       <c r="G70" s="12" t="str">
-        <f aca="false">IF(C70="idle","n/a",IF(C70=D70,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H70" s="15"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12" t="n">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A71" s="12">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="n">
+      <c r="B71" s="12">
         <v>2</v>
       </c>
       <c r="C71" s="12" t="s">
@@ -2909,23 +2813,23 @@
       <c r="D71" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E71" s="13">
         <v>0.76</v>
       </c>
-      <c r="F71" s="14" t="n">
+      <c r="F71" s="14">
         <v>0.02</v>
       </c>
       <c r="G71" s="12" t="str">
-        <f aca="false">IF(C71="idle","n/a",IF(C71=D71,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H71" s="15"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="n">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A72" s="12">
         <v>71</v>
       </c>
-      <c r="B72" s="12" t="n">
+      <c r="B72" s="12">
         <v>2</v>
       </c>
       <c r="C72" s="12" t="s">
@@ -2934,23 +2838,23 @@
       <c r="D72" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="13" t="n">
+      <c r="E72" s="13">
         <v>0.75</v>
       </c>
-      <c r="F72" s="14" t="n">
+      <c r="F72" s="14">
         <v>0.05</v>
       </c>
       <c r="G72" s="12" t="str">
-        <f aca="false">IF(C72="idle","n/a",IF(C72=D72,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H72" s="15"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="n">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A73" s="12">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="12">
         <v>2</v>
       </c>
       <c r="C73" s="12" t="s">
@@ -2959,23 +2863,23 @@
       <c r="D73" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E73" s="13" t="n">
+      <c r="E73" s="13">
         <v>0.89</v>
       </c>
-      <c r="F73" s="14" t="n">
+      <c r="F73" s="14">
         <v>0.04</v>
       </c>
       <c r="G73" s="12" t="str">
-        <f aca="false">IF(C73="idle","n/a",IF(C73=D73,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H73" s="15"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="n">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A74" s="12">
         <v>73</v>
       </c>
-      <c r="B74" s="12" t="n">
+      <c r="B74" s="12">
         <v>2</v>
       </c>
       <c r="C74" s="12" t="s">
@@ -2984,23 +2888,23 @@
       <c r="D74" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E74" s="13" t="n">
+      <c r="E74" s="13">
         <v>0.87</v>
       </c>
-      <c r="F74" s="14" t="n">
+      <c r="F74" s="14">
         <v>0.06</v>
       </c>
       <c r="G74" s="12" t="str">
-        <f aca="false">IF(C74="idle","n/a",IF(C74=D74,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H74" s="15"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="n">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A75" s="12">
         <v>74</v>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="12">
         <v>2</v>
       </c>
       <c r="C75" s="12" t="s">
@@ -3009,23 +2913,23 @@
       <c r="D75" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E75" s="13" t="n">
+      <c r="E75" s="13">
         <v>0.81</v>
       </c>
-      <c r="F75" s="14" t="n">
+      <c r="F75" s="14">
         <v>0.05</v>
       </c>
       <c r="G75" s="12" t="str">
-        <f aca="false">IF(C75="idle","n/a",IF(C75=D75,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H75" s="15"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12" t="n">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A76" s="12">
         <v>75</v>
       </c>
-      <c r="B76" s="12" t="n">
+      <c r="B76" s="12">
         <v>2</v>
       </c>
       <c r="C76" s="12" t="s">
@@ -3034,23 +2938,23 @@
       <c r="D76" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F76" s="14" t="n">
+      <c r="E76" s="13">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F76" s="14">
         <v>0.06</v>
       </c>
       <c r="G76" s="12" t="str">
-        <f aca="false">IF(C76="idle","n/a",IF(C76=D76,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H76" s="15"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12" t="n">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A77" s="12">
         <v>76</v>
       </c>
-      <c r="B77" s="12" t="n">
+      <c r="B77" s="12">
         <v>2</v>
       </c>
       <c r="C77" s="12" t="s">
@@ -3059,23 +2963,23 @@
       <c r="D77" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E77" s="13" t="n">
+      <c r="E77" s="13">
         <v>0.41</v>
       </c>
-      <c r="F77" s="14" t="n">
+      <c r="F77" s="14">
         <v>0.04</v>
       </c>
       <c r="G77" s="12" t="str">
-        <f aca="false">IF(C77="idle","n/a",IF(C77=D77,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H77" s="15"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="12" t="n">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A78" s="12">
         <v>77</v>
       </c>
-      <c r="B78" s="12" t="n">
+      <c r="B78" s="12">
         <v>2</v>
       </c>
       <c r="C78" s="12" t="s">
@@ -3084,23 +2988,23 @@
       <c r="D78" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="13" t="n">
+      <c r="E78" s="13">
         <v>0.93</v>
       </c>
-      <c r="F78" s="14" t="n">
-        <v>0.07</v>
+      <c r="F78" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G78" s="12" t="str">
-        <f aca="false">IF(C78="idle","n/a",IF(C78=D78,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H78" s="15"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="12" t="n">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A79" s="12">
         <v>78</v>
       </c>
-      <c r="B79" s="12" t="n">
+      <c r="B79" s="12">
         <v>2</v>
       </c>
       <c r="C79" s="12" t="s">
@@ -3109,23 +3013,23 @@
       <c r="D79" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E79" s="13" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="F79" s="14" t="n">
+      <c r="E79" s="13">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F79" s="14">
         <v>0.05</v>
       </c>
       <c r="G79" s="12" t="str">
-        <f aca="false">IF(C79="idle","n/a",IF(C79=D79,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H79" s="15"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="12" t="n">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A80" s="12">
         <v>79</v>
       </c>
-      <c r="B80" s="12" t="n">
+      <c r="B80" s="12">
         <v>2</v>
       </c>
       <c r="C80" s="12" t="s">
@@ -3134,23 +3038,23 @@
       <c r="D80" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E80" s="13" t="n">
+      <c r="E80" s="13">
         <v>0.95</v>
       </c>
-      <c r="F80" s="14" t="n">
+      <c r="F80" s="14">
         <v>0.04</v>
       </c>
       <c r="G80" s="12" t="str">
-        <f aca="false">IF(C80="idle","n/a",IF(C80=D80,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H80" s="15"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="12" t="n">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A81" s="12">
         <v>80</v>
       </c>
-      <c r="B81" s="12" t="n">
+      <c r="B81" s="12">
         <v>2</v>
       </c>
       <c r="C81" s="12" t="s">
@@ -3159,23 +3063,23 @@
       <c r="D81" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E81" s="13" t="n">
+      <c r="E81" s="13">
         <v>0.92</v>
       </c>
-      <c r="F81" s="14" t="n">
+      <c r="F81" s="14">
         <v>0.04</v>
       </c>
       <c r="G81" s="12" t="str">
-        <f aca="false">IF(C81="idle","n/a",IF(C81=D81,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H81" s="15"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="12" t="n">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A82" s="12">
         <v>81</v>
       </c>
-      <c r="B82" s="12" t="n">
+      <c r="B82" s="12">
         <v>2</v>
       </c>
       <c r="C82" s="12" t="s">
@@ -3184,23 +3088,23 @@
       <c r="D82" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E82" s="13">
         <v>0.61</v>
       </c>
-      <c r="F82" s="14" t="n">
+      <c r="F82" s="14">
         <v>0.06</v>
       </c>
       <c r="G82" s="12" t="str">
-        <f aca="false">IF(C82="idle","n/a",IF(C82=D82,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H82" s="15"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12" t="n">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A83" s="12">
         <v>82</v>
       </c>
-      <c r="B83" s="12" t="n">
+      <c r="B83" s="12">
         <v>2</v>
       </c>
       <c r="C83" s="12" t="s">
@@ -3209,23 +3113,23 @@
       <c r="D83" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E83" s="13" t="n">
+      <c r="E83" s="13">
         <v>0.79</v>
       </c>
-      <c r="F83" s="14" t="n">
+      <c r="F83" s="14">
         <v>0.06</v>
       </c>
       <c r="G83" s="12" t="str">
-        <f aca="false">IF(C83="idle","n/a",IF(C83=D83,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H83" s="15"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="12" t="n">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A84" s="12">
         <v>83</v>
       </c>
-      <c r="B84" s="12" t="n">
+      <c r="B84" s="12">
         <v>2</v>
       </c>
       <c r="C84" s="12" t="s">
@@ -3234,23 +3138,23 @@
       <c r="D84" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E84" s="13" t="n">
+      <c r="E84" s="13">
         <v>0.96</v>
       </c>
-      <c r="F84" s="14" t="n">
+      <c r="F84" s="14">
         <v>0.06</v>
       </c>
       <c r="G84" s="12" t="str">
-        <f aca="false">IF(C84="idle","n/a",IF(C84=D84,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H84" s="15"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12" t="n">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A85" s="12">
         <v>84</v>
       </c>
-      <c r="B85" s="12" t="n">
+      <c r="B85" s="12">
         <v>2</v>
       </c>
       <c r="C85" s="12" t="s">
@@ -3259,23 +3163,23 @@
       <c r="D85" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E85" s="13" t="n">
+      <c r="E85" s="13">
         <v>0.92</v>
       </c>
-      <c r="F85" s="14" t="n">
+      <c r="F85" s="14">
         <v>0.06</v>
       </c>
       <c r="G85" s="12" t="str">
-        <f aca="false">IF(C85="idle","n/a",IF(C85=D85,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H85" s="15"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="12" t="n">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A86" s="12">
         <v>85</v>
       </c>
-      <c r="B86" s="12" t="n">
+      <c r="B86" s="12">
         <v>2</v>
       </c>
       <c r="C86" s="12" t="s">
@@ -3284,23 +3188,23 @@
       <c r="D86" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E86" s="13" t="n">
+      <c r="E86" s="13">
         <v>0.98</v>
       </c>
-      <c r="F86" s="14" t="n">
+      <c r="F86" s="14">
         <v>0.04</v>
       </c>
       <c r="G86" s="12" t="str">
-        <f aca="false">IF(C86="idle","n/a",IF(C86=D86,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H86" s="15"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="12" t="n">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A87" s="12">
         <v>86</v>
       </c>
-      <c r="B87" s="12" t="n">
+      <c r="B87" s="12">
         <v>2</v>
       </c>
       <c r="C87" s="12" t="s">
@@ -3309,23 +3213,23 @@
       <c r="D87" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E87" s="13" t="n">
+      <c r="E87" s="13">
         <v>0.94</v>
       </c>
-      <c r="F87" s="14" t="n">
+      <c r="F87" s="14">
         <v>0.06</v>
       </c>
       <c r="G87" s="12" t="str">
-        <f aca="false">IF(C87="idle","n/a",IF(C87=D87,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H87" s="15"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="12" t="n">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A88" s="12">
         <v>87</v>
       </c>
-      <c r="B88" s="12" t="n">
+      <c r="B88" s="12">
         <v>2</v>
       </c>
       <c r="C88" s="12" t="s">
@@ -3334,23 +3238,23 @@
       <c r="D88" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E88" s="13" t="n">
+      <c r="E88" s="13">
         <v>0.95</v>
       </c>
-      <c r="F88" s="14" t="n">
-        <v>0.07</v>
+      <c r="F88" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G88" s="12" t="str">
-        <f aca="false">IF(C88="idle","n/a",IF(C88=D88,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H88" s="15"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12" t="n">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A89" s="12">
         <v>88</v>
       </c>
-      <c r="B89" s="12" t="n">
+      <c r="B89" s="12">
         <v>2</v>
       </c>
       <c r="C89" s="12" t="s">
@@ -3359,23 +3263,23 @@
       <c r="D89" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E89" s="13" t="n">
+      <c r="E89" s="13">
         <v>0.39</v>
       </c>
-      <c r="F89" s="14" t="n">
+      <c r="F89" s="14">
         <v>0.03</v>
       </c>
       <c r="G89" s="12" t="str">
-        <f aca="false">IF(C89="idle","n/a",IF(C89=D89,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H89" s="15"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="12" t="n">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A90" s="12">
         <v>89</v>
       </c>
-      <c r="B90" s="12" t="n">
+      <c r="B90" s="12">
         <v>2</v>
       </c>
       <c r="C90" s="12" t="s">
@@ -3384,23 +3288,23 @@
       <c r="D90" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E90" s="13" t="n">
+      <c r="E90" s="13">
         <v>0.3</v>
       </c>
-      <c r="F90" s="14" t="n">
+      <c r="F90" s="14">
         <v>0.02</v>
       </c>
       <c r="G90" s="12" t="str">
-        <f aca="false">IF(C90="idle","n/a",IF(C90=D90,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>No</v>
       </c>
       <c r="H90" s="15"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="12" t="n">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A91" s="12">
         <v>90</v>
       </c>
-      <c r="B91" s="12" t="n">
+      <c r="B91" s="12">
         <v>2</v>
       </c>
       <c r="C91" s="12" t="s">
@@ -3409,23 +3313,23 @@
       <c r="D91" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="13" t="n">
+      <c r="E91" s="13">
         <v>0.99</v>
       </c>
-      <c r="F91" s="14" t="n">
+      <c r="F91" s="14">
         <v>0.06</v>
       </c>
       <c r="G91" s="12" t="str">
-        <f aca="false">IF(C91="idle","n/a",IF(C91=D91,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H91" s="15"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="12" t="n">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A92" s="12">
         <v>91</v>
       </c>
-      <c r="B92" s="12" t="n">
+      <c r="B92" s="12">
         <v>2</v>
       </c>
       <c r="C92" s="12" t="s">
@@ -3434,23 +3338,23 @@
       <c r="D92" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E92" s="13" t="n">
+      <c r="E92" s="13">
         <v>0.99</v>
       </c>
-      <c r="F92" s="14" t="n">
-        <v>0.07</v>
+      <c r="F92" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G92" s="12" t="str">
-        <f aca="false">IF(C92="idle","n/a",IF(C92=D92,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H92" s="15"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="12" t="n">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A93" s="12">
         <v>92</v>
       </c>
-      <c r="B93" s="12" t="n">
+      <c r="B93" s="12">
         <v>2</v>
       </c>
       <c r="C93" s="12" t="s">
@@ -3459,23 +3363,23 @@
       <c r="D93" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E93" s="13" t="n">
+      <c r="E93" s="13">
         <v>0.98</v>
       </c>
-      <c r="F93" s="14" t="n">
+      <c r="F93" s="14">
         <v>0.06</v>
       </c>
       <c r="G93" s="12" t="str">
-        <f aca="false">IF(C93="idle","n/a",IF(C93=D93,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H93" s="15"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="12" t="n">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A94" s="12">
         <v>93</v>
       </c>
-      <c r="B94" s="12" t="n">
+      <c r="B94" s="12">
         <v>2</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -3484,23 +3388,23 @@
       <c r="D94" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E94" s="13" t="n">
+      <c r="E94" s="13">
         <v>0.98</v>
       </c>
-      <c r="F94" s="14" t="n">
-        <v>0.07</v>
+      <c r="F94" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G94" s="12" t="str">
-        <f aca="false">IF(C94="idle","n/a",IF(C94=D94,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H94" s="15"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="12" t="n">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A95" s="12">
         <v>94</v>
       </c>
-      <c r="B95" s="12" t="n">
+      <c r="B95" s="12">
         <v>2</v>
       </c>
       <c r="C95" s="12" t="s">
@@ -3509,23 +3413,23 @@
       <c r="D95" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E95" s="13" t="n">
+      <c r="E95" s="13">
         <v>0.82</v>
       </c>
-      <c r="F95" s="14" t="n">
-        <v>0.07</v>
+      <c r="F95" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G95" s="12" t="str">
-        <f aca="false">IF(C95="idle","n/a",IF(C95=D95,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H95" s="15"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="12" t="n">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A96" s="12">
         <v>95</v>
       </c>
-      <c r="B96" s="12" t="n">
+      <c r="B96" s="12">
         <v>2</v>
       </c>
       <c r="C96" s="12" t="s">
@@ -3534,23 +3438,23 @@
       <c r="D96" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E96" s="13" t="n">
+      <c r="E96" s="13">
         <v>0.96</v>
       </c>
-      <c r="F96" s="14" t="n">
+      <c r="F96" s="14">
         <v>0.09</v>
       </c>
       <c r="G96" s="12" t="str">
-        <f aca="false">IF(C96="idle","n/a",IF(C96=D96,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H96" s="15"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="12" t="n">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A97" s="12">
         <v>96</v>
       </c>
-      <c r="B97" s="12" t="n">
+      <c r="B97" s="12">
         <v>2</v>
       </c>
       <c r="C97" s="12" t="s">
@@ -3559,23 +3463,23 @@
       <c r="D97" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E97" s="13" t="n">
+      <c r="E97" s="13">
         <v>0.96</v>
       </c>
-      <c r="F97" s="14" t="n">
+      <c r="F97" s="14">
         <v>0.05</v>
       </c>
       <c r="G97" s="12" t="str">
-        <f aca="false">IF(C97="idle","n/a",IF(C97=D97,"Yes","No"))</f>
+        <f t="shared" si="2"/>
         <v>Yes</v>
       </c>
       <c r="H97" s="15"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="12" t="n">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A98" s="12">
         <v>97</v>
       </c>
-      <c r="B98" s="12" t="n">
+      <c r="B98" s="12">
         <v>2</v>
       </c>
       <c r="C98" s="12" t="s">
@@ -3584,23 +3488,23 @@
       <c r="D98" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E98" s="13" t="n">
+      <c r="E98" s="13">
         <v>0.98</v>
       </c>
-      <c r="F98" s="14" t="n">
+      <c r="F98" s="14">
         <v>0.06</v>
       </c>
       <c r="G98" s="12" t="str">
-        <f aca="false">IF(C98="idle","n/a",IF(C98=D98,"Yes","No"))</f>
+        <f t="shared" ref="G98:G129" si="3">IF(C98="idle","n/a",IF(C98=D98,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="H98" s="15"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="12" t="n">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A99" s="12">
         <v>98</v>
       </c>
-      <c r="B99" s="12" t="n">
+      <c r="B99" s="12">
         <v>2</v>
       </c>
       <c r="C99" s="12" t="s">
@@ -3609,23 +3513,23 @@
       <c r="D99" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E99" s="13" t="n">
+      <c r="E99" s="13">
         <v>0.98</v>
       </c>
-      <c r="F99" s="14" t="n">
+      <c r="F99" s="14">
         <v>0.08</v>
       </c>
       <c r="G99" s="12" t="str">
-        <f aca="false">IF(C99="idle","n/a",IF(C99=D99,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H99" s="15"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="12" t="n">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A100" s="12">
         <v>99</v>
       </c>
-      <c r="B100" s="12" t="n">
+      <c r="B100" s="12">
         <v>2</v>
       </c>
       <c r="C100" s="12" t="s">
@@ -3634,23 +3538,23 @@
       <c r="D100" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E100" s="13" t="n">
+      <c r="E100" s="13">
         <v>0.99</v>
       </c>
-      <c r="F100" s="14" t="n">
-        <v>0.07</v>
+      <c r="F100" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G100" s="12" t="str">
-        <f aca="false">IF(C100="idle","n/a",IF(C100=D100,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H100" s="15"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="12" t="n">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A101" s="12">
         <v>100</v>
       </c>
-      <c r="B101" s="12" t="n">
+      <c r="B101" s="12">
         <v>2</v>
       </c>
       <c r="C101" s="12" t="s">
@@ -3659,23 +3563,23 @@
       <c r="D101" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E101" s="13" t="n">
+      <c r="E101" s="13">
         <v>0.96</v>
       </c>
-      <c r="F101" s="14" t="n">
-        <v>0.07</v>
+      <c r="F101" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G101" s="12" t="str">
-        <f aca="false">IF(C101="idle","n/a",IF(C101=D101,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H101" s="15"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="12" t="n">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A102" s="12">
         <v>101</v>
       </c>
-      <c r="B102" s="12" t="n">
+      <c r="B102" s="12">
         <v>2</v>
       </c>
       <c r="C102" s="12" t="s">
@@ -3684,25 +3588,25 @@
       <c r="D102" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E102" s="13" t="n">
+      <c r="E102" s="13">
         <v>0.24</v>
       </c>
-      <c r="F102" s="14" t="n">
+      <c r="F102" s="14">
         <v>0.03</v>
       </c>
       <c r="G102" s="12" t="str">
-        <f aca="false">IF(C102="idle","n/a",IF(C102=D102,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="H102" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="12" t="n">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A103" s="12">
         <v>102</v>
       </c>
-      <c r="B103" s="12" t="n">
+      <c r="B103" s="12">
         <v>2</v>
       </c>
       <c r="C103" s="12" t="s">
@@ -3711,23 +3615,23 @@
       <c r="D103" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E103" s="13" t="n">
+      <c r="E103" s="13">
         <v>0.97</v>
       </c>
-      <c r="F103" s="14" t="n">
+      <c r="F103" s="14">
         <v>0.06</v>
       </c>
       <c r="G103" s="12" t="str">
-        <f aca="false">IF(C103="idle","n/a",IF(C103=D103,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H103" s="15"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="12" t="n">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A104" s="12">
         <v>103</v>
       </c>
-      <c r="B104" s="12" t="n">
+      <c r="B104" s="12">
         <v>2</v>
       </c>
       <c r="C104" s="12" t="s">
@@ -3736,23 +3640,23 @@
       <c r="D104" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E104" s="13" t="n">
+      <c r="E104" s="13">
         <v>0.99</v>
       </c>
-      <c r="F104" s="14" t="n">
+      <c r="F104" s="14">
         <v>0.08</v>
       </c>
       <c r="G104" s="12" t="str">
-        <f aca="false">IF(C104="idle","n/a",IF(C104=D104,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H104" s="15"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="12" t="n">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A105" s="12">
         <v>104</v>
       </c>
-      <c r="B105" s="12" t="n">
+      <c r="B105" s="12">
         <v>2</v>
       </c>
       <c r="C105" s="12" t="s">
@@ -3761,23 +3665,23 @@
       <c r="D105" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E105" s="13" t="n">
+      <c r="E105" s="13">
         <v>0.99</v>
       </c>
-      <c r="F105" s="14" t="n">
-        <v>0.07</v>
+      <c r="F105" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G105" s="12" t="str">
-        <f aca="false">IF(C105="idle","n/a",IF(C105=D105,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H105" s="15"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="12" t="n">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A106" s="12">
         <v>105</v>
       </c>
-      <c r="B106" s="12" t="n">
+      <c r="B106" s="12">
         <v>2</v>
       </c>
       <c r="C106" s="12" t="s">
@@ -3786,23 +3690,23 @@
       <c r="D106" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E106" s="13" t="n">
+      <c r="E106" s="13">
         <v>0.87</v>
       </c>
-      <c r="F106" s="14" t="n">
+      <c r="F106" s="14">
         <v>0.06</v>
       </c>
       <c r="G106" s="12" t="str">
-        <f aca="false">IF(C106="idle","n/a",IF(C106=D106,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H106" s="15"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="12" t="n">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A107" s="12">
         <v>106</v>
       </c>
-      <c r="B107" s="12" t="n">
+      <c r="B107" s="12">
         <v>2</v>
       </c>
       <c r="C107" s="12" t="s">
@@ -3811,23 +3715,23 @@
       <c r="D107" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E107" s="13" t="n">
+      <c r="E107" s="13">
         <v>0.4</v>
       </c>
-      <c r="F107" s="14" t="n">
+      <c r="F107" s="14">
         <v>0.04</v>
       </c>
       <c r="G107" s="12" t="str">
-        <f aca="false">IF(C107="idle","n/a",IF(C107=D107,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H107" s="15"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="12" t="n">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A108" s="12">
         <v>107</v>
       </c>
-      <c r="B108" s="12" t="n">
+      <c r="B108" s="12">
         <v>2</v>
       </c>
       <c r="C108" s="12" t="s">
@@ -3836,23 +3740,23 @@
       <c r="D108" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E108" s="13" t="n">
+      <c r="E108" s="13">
         <v>0.93</v>
       </c>
-      <c r="F108" s="14" t="n">
+      <c r="F108" s="14">
         <v>0.09</v>
       </c>
       <c r="G108" s="12" t="str">
-        <f aca="false">IF(C108="idle","n/a",IF(C108=D108,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H108" s="15"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="12" t="n">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A109" s="12">
         <v>108</v>
       </c>
-      <c r="B109" s="12" t="n">
+      <c r="B109" s="12">
         <v>2</v>
       </c>
       <c r="C109" s="12" t="s">
@@ -3861,23 +3765,23 @@
       <c r="D109" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E109" s="13" t="n">
+      <c r="E109" s="13">
         <v>0.89</v>
       </c>
-      <c r="F109" s="14" t="n">
+      <c r="F109" s="14">
         <v>0.06</v>
       </c>
       <c r="G109" s="12" t="str">
-        <f aca="false">IF(C109="idle","n/a",IF(C109=D109,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H109" s="15"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="12" t="n">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A110" s="12">
         <v>109</v>
       </c>
-      <c r="B110" s="12" t="n">
+      <c r="B110" s="12">
         <v>2</v>
       </c>
       <c r="C110" s="12" t="s">
@@ -3886,23 +3790,23 @@
       <c r="D110" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E110" s="13" t="n">
+      <c r="E110" s="13">
         <v>0.98</v>
       </c>
-      <c r="F110" s="14" t="n">
+      <c r="F110" s="14">
         <v>0.06</v>
       </c>
       <c r="G110" s="12" t="str">
-        <f aca="false">IF(C110="idle","n/a",IF(C110=D110,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H110" s="15"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="12" t="n">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A111" s="12">
         <v>110</v>
       </c>
-      <c r="B111" s="12" t="n">
+      <c r="B111" s="12">
         <v>2</v>
       </c>
       <c r="C111" s="12" t="s">
@@ -3911,23 +3815,23 @@
       <c r="D111" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E111" s="13" t="n">
+      <c r="E111" s="13">
         <v>0.99</v>
       </c>
-      <c r="F111" s="14" t="n">
+      <c r="F111" s="14">
         <v>0.05</v>
       </c>
       <c r="G111" s="12" t="str">
-        <f aca="false">IF(C111="idle","n/a",IF(C111=D111,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H111" s="15"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="12" t="n">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A112" s="12">
         <v>111</v>
       </c>
-      <c r="B112" s="12" t="n">
+      <c r="B112" s="12">
         <v>2</v>
       </c>
       <c r="C112" s="12" t="s">
@@ -3936,23 +3840,23 @@
       <c r="D112" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E112" s="13" t="n">
+      <c r="E112" s="13">
         <v>0.97</v>
       </c>
-      <c r="F112" s="14" t="n">
+      <c r="F112" s="14">
         <v>0.06</v>
       </c>
       <c r="G112" s="12" t="str">
-        <f aca="false">IF(C112="idle","n/a",IF(C112=D112,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H112" s="15"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="12" t="n">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A113" s="12">
         <v>112</v>
       </c>
-      <c r="B113" s="12" t="n">
+      <c r="B113" s="12">
         <v>2</v>
       </c>
       <c r="C113" s="12" t="s">
@@ -3961,23 +3865,23 @@
       <c r="D113" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="13" t="n">
+      <c r="E113" s="13">
         <v>0.99</v>
       </c>
-      <c r="F113" s="14" t="n">
+      <c r="F113" s="14">
         <v>0.05</v>
       </c>
       <c r="G113" s="12" t="str">
-        <f aca="false">IF(C113="idle","n/a",IF(C113=D113,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H113" s="15"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="12" t="n">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A114" s="12">
         <v>113</v>
       </c>
-      <c r="B114" s="12" t="n">
+      <c r="B114" s="12">
         <v>2</v>
       </c>
       <c r="C114" s="12" t="s">
@@ -3986,23 +3890,23 @@
       <c r="D114" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E114" s="13" t="n">
+      <c r="E114" s="13">
         <v>0.35</v>
       </c>
-      <c r="F114" s="14" t="n">
+      <c r="F114" s="14">
         <v>0.02</v>
       </c>
       <c r="G114" s="12" t="str">
-        <f aca="false">IF(C114="idle","n/a",IF(C114=D114,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H114" s="15"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="12" t="n">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A115" s="12">
         <v>114</v>
       </c>
-      <c r="B115" s="12" t="n">
+      <c r="B115" s="12">
         <v>2</v>
       </c>
       <c r="C115" s="12" t="s">
@@ -4011,23 +3915,23 @@
       <c r="D115" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E115" s="13" t="n">
+      <c r="E115" s="13">
         <v>0.68</v>
       </c>
-      <c r="F115" s="14" t="n">
+      <c r="F115" s="14">
         <v>0.08</v>
       </c>
       <c r="G115" s="12" t="str">
-        <f aca="false">IF(C115="idle","n/a",IF(C115=D115,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H115" s="15"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="12" t="n">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A116" s="12">
         <v>115</v>
       </c>
-      <c r="B116" s="12" t="n">
+      <c r="B116" s="12">
         <v>2</v>
       </c>
       <c r="C116" s="12" t="s">
@@ -4036,23 +3940,23 @@
       <c r="D116" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E116" s="13" t="n">
+      <c r="E116" s="13">
         <v>0.65</v>
       </c>
-      <c r="F116" s="14" t="n">
+      <c r="F116" s="14">
         <v>0.08</v>
       </c>
       <c r="G116" s="12" t="str">
-        <f aca="false">IF(C116="idle","n/a",IF(C116=D116,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H116" s="15"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="12" t="n">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A117" s="12">
         <v>116</v>
       </c>
-      <c r="B117" s="12" t="n">
+      <c r="B117" s="12">
         <v>2</v>
       </c>
       <c r="C117" s="12" t="s">
@@ -4061,23 +3965,23 @@
       <c r="D117" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E117" s="13" t="n">
+      <c r="E117" s="13">
         <v>0.98</v>
       </c>
-      <c r="F117" s="14" t="n">
+      <c r="F117" s="14">
         <v>0.06</v>
       </c>
       <c r="G117" s="12" t="str">
-        <f aca="false">IF(C117="idle","n/a",IF(C117=D117,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H117" s="15"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="12" t="n">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A118" s="12">
         <v>117</v>
       </c>
-      <c r="B118" s="12" t="n">
+      <c r="B118" s="12">
         <v>2</v>
       </c>
       <c r="C118" s="12" t="s">
@@ -4086,23 +3990,23 @@
       <c r="D118" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E118" s="13" t="n">
+      <c r="E118" s="13">
         <v>0.97</v>
       </c>
-      <c r="F118" s="14" t="n">
+      <c r="F118" s="14">
         <v>0.06</v>
       </c>
       <c r="G118" s="12" t="str">
-        <f aca="false">IF(C118="idle","n/a",IF(C118=D118,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H118" s="15"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="12" t="n">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A119" s="12">
         <v>118</v>
       </c>
-      <c r="B119" s="12" t="n">
+      <c r="B119" s="12">
         <v>2</v>
       </c>
       <c r="C119" s="12" t="s">
@@ -4111,23 +4015,23 @@
       <c r="D119" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E119" s="13" t="n">
+      <c r="E119" s="13">
         <v>0.81</v>
       </c>
-      <c r="F119" s="14" t="n">
+      <c r="F119" s="14">
         <v>0.05</v>
       </c>
       <c r="G119" s="12" t="str">
-        <f aca="false">IF(C119="idle","n/a",IF(C119=D119,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H119" s="15"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="12" t="n">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A120" s="12">
         <v>119</v>
       </c>
-      <c r="B120" s="12" t="n">
+      <c r="B120" s="12">
         <v>2</v>
       </c>
       <c r="C120" s="12" t="s">
@@ -4136,23 +4040,23 @@
       <c r="D120" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E120" s="13" t="n">
+      <c r="E120" s="13">
         <v>0.85</v>
       </c>
-      <c r="F120" s="14" t="n">
+      <c r="F120" s="14">
         <v>0.06</v>
       </c>
       <c r="G120" s="12" t="str">
-        <f aca="false">IF(C120="idle","n/a",IF(C120=D120,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H120" s="15"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="12" t="n">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A121" s="12">
         <v>120</v>
       </c>
-      <c r="B121" s="12" t="n">
+      <c r="B121" s="12">
         <v>2</v>
       </c>
       <c r="C121" s="12" t="s">
@@ -4161,23 +4065,23 @@
       <c r="D121" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E121" s="13" t="n">
+      <c r="E121" s="13">
         <v>0.97</v>
       </c>
-      <c r="F121" s="14" t="n">
+      <c r="F121" s="14">
         <v>0.09</v>
       </c>
       <c r="G121" s="12" t="str">
-        <f aca="false">IF(C121="idle","n/a",IF(C121=D121,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H121" s="15"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="12" t="n">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A122" s="12">
         <v>121</v>
       </c>
-      <c r="B122" s="12" t="n">
+      <c r="B122" s="12">
         <v>2</v>
       </c>
       <c r="C122" s="12" t="s">
@@ -4186,23 +4090,23 @@
       <c r="D122" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E122" s="13" t="n">
+      <c r="E122" s="13">
         <v>0.98</v>
       </c>
-      <c r="F122" s="14" t="n">
+      <c r="F122" s="14">
         <v>0.06</v>
       </c>
       <c r="G122" s="12" t="str">
-        <f aca="false">IF(C122="idle","n/a",IF(C122=D122,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H122" s="15"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="12" t="n">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A123" s="12">
         <v>122</v>
       </c>
-      <c r="B123" s="12" t="n">
+      <c r="B123" s="12">
         <v>2</v>
       </c>
       <c r="C123" s="12" t="s">
@@ -4211,23 +4115,23 @@
       <c r="D123" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E123" s="13" t="n">
+      <c r="E123" s="13">
         <v>0.99</v>
       </c>
-      <c r="F123" s="14" t="n">
-        <v>0.07</v>
+      <c r="F123" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G123" s="12" t="str">
-        <f aca="false">IF(C123="idle","n/a",IF(C123=D123,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H123" s="15"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="12" t="n">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A124" s="12">
         <v>123</v>
       </c>
-      <c r="B124" s="12" t="n">
+      <c r="B124" s="12">
         <v>2</v>
       </c>
       <c r="C124" s="12" t="s">
@@ -4236,23 +4140,23 @@
       <c r="D124" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E124" s="13" t="n">
+      <c r="E124" s="13">
         <v>0.91</v>
       </c>
-      <c r="F124" s="14" t="n">
+      <c r="F124" s="14">
         <v>0.08</v>
       </c>
       <c r="G124" s="12" t="str">
-        <f aca="false">IF(C124="idle","n/a",IF(C124=D124,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H124" s="15"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="12" t="n">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A125" s="12">
         <v>124</v>
       </c>
-      <c r="B125" s="12" t="n">
+      <c r="B125" s="12">
         <v>2</v>
       </c>
       <c r="C125" s="12" t="s">
@@ -4261,23 +4165,23 @@
       <c r="D125" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E125" s="13" t="n">
+      <c r="E125" s="13">
         <v>0.86</v>
       </c>
-      <c r="F125" s="14" t="n">
+      <c r="F125" s="14">
         <v>0.06</v>
       </c>
       <c r="G125" s="12" t="str">
-        <f aca="false">IF(C125="idle","n/a",IF(C125=D125,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H125" s="15"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="12" t="n">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A126" s="12">
         <v>125</v>
       </c>
-      <c r="B126" s="12" t="n">
+      <c r="B126" s="12">
         <v>2</v>
       </c>
       <c r="C126" s="12" t="s">
@@ -4286,23 +4190,23 @@
       <c r="D126" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E126" s="13" t="n">
+      <c r="E126" s="13">
         <v>0.98</v>
       </c>
-      <c r="F126" s="14" t="n">
+      <c r="F126" s="14">
         <v>0.08</v>
       </c>
       <c r="G126" s="12" t="str">
-        <f aca="false">IF(C126="idle","n/a",IF(C126=D126,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H126" s="15"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="12" t="n">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A127" s="12">
         <v>126</v>
       </c>
-      <c r="B127" s="12" t="n">
+      <c r="B127" s="12">
         <v>2</v>
       </c>
       <c r="C127" s="12" t="s">
@@ -4311,23 +4215,23 @@
       <c r="D127" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E127" s="13" t="n">
+      <c r="E127" s="13">
         <v>0.98</v>
       </c>
-      <c r="F127" s="14" t="n">
+      <c r="F127" s="14">
         <v>0.08</v>
       </c>
       <c r="G127" s="12" t="str">
-        <f aca="false">IF(C127="idle","n/a",IF(C127=D127,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H127" s="15"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="12" t="n">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A128" s="12">
         <v>127</v>
       </c>
-      <c r="B128" s="12" t="n">
+      <c r="B128" s="12">
         <v>2</v>
       </c>
       <c r="C128" s="12" t="s">
@@ -4336,23 +4240,23 @@
       <c r="D128" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E128" s="13" t="n">
+      <c r="E128" s="13">
         <v>0.99</v>
       </c>
-      <c r="F128" s="14" t="n">
+      <c r="F128" s="14">
         <v>0.13</v>
       </c>
       <c r="G128" s="12" t="str">
-        <f aca="false">IF(C128="idle","n/a",IF(C128=D128,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="H128" s="15"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="12" t="n">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A129" s="12">
         <v>128</v>
       </c>
-      <c r="B129" s="12" t="n">
+      <c r="B129" s="12">
         <v>2</v>
       </c>
       <c r="C129" s="12" t="s">
@@ -4361,25 +4265,25 @@
       <c r="D129" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E129" s="13" t="n">
+      <c r="E129" s="13">
         <v>0.45</v>
       </c>
-      <c r="F129" s="14" t="n">
+      <c r="F129" s="14">
         <v>0.11</v>
       </c>
       <c r="G129" s="12" t="str">
-        <f aca="false">IF(C129="idle","n/a",IF(C129=D129,"Yes","No"))</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="H129" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="12" t="n">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A130" s="12">
         <v>129</v>
       </c>
-      <c r="B130" s="12" t="n">
+      <c r="B130" s="12">
         <v>2</v>
       </c>
       <c r="C130" s="12" t="s">
@@ -4388,23 +4292,23 @@
       <c r="D130" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E130" s="13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F130" s="14" t="n">
+      <c r="E130" s="13">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F130" s="14">
         <v>0.03</v>
       </c>
       <c r="G130" s="12" t="str">
-        <f aca="false">IF(C130="idle","n/a",IF(C130=D130,"Yes","No"))</f>
+        <f t="shared" ref="G130:G161" si="4">IF(C130="idle","n/a",IF(C130=D130,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="H130" s="15"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="12" t="n">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A131" s="12">
         <v>130</v>
       </c>
-      <c r="B131" s="12" t="n">
+      <c r="B131" s="12">
         <v>2</v>
       </c>
       <c r="C131" s="12" t="s">
@@ -4413,23 +4317,23 @@
       <c r="D131" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E131" s="13" t="n">
+      <c r="E131" s="13">
         <v>0.97</v>
       </c>
-      <c r="F131" s="14" t="n">
+      <c r="F131" s="14">
         <v>0.11</v>
       </c>
       <c r="G131" s="12" t="str">
-        <f aca="false">IF(C131="idle","n/a",IF(C131=D131,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H131" s="15"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="12" t="n">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A132" s="12">
         <v>131</v>
       </c>
-      <c r="B132" s="12" t="n">
+      <c r="B132" s="12">
         <v>2</v>
       </c>
       <c r="C132" s="12" t="s">
@@ -4438,23 +4342,23 @@
       <c r="D132" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E132" s="13" t="n">
+      <c r="E132" s="13">
         <v>0.98</v>
       </c>
-      <c r="F132" s="14" t="n">
+      <c r="F132" s="14">
         <v>0.09</v>
       </c>
       <c r="G132" s="12" t="str">
-        <f aca="false">IF(C132="idle","n/a",IF(C132=D132,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H132" s="15"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="12" t="n">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A133" s="12">
         <v>132</v>
       </c>
-      <c r="B133" s="12" t="n">
+      <c r="B133" s="12">
         <v>2</v>
       </c>
       <c r="C133" s="12" t="s">
@@ -4463,23 +4367,23 @@
       <c r="D133" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E133" s="13" t="n">
+      <c r="E133" s="13">
         <v>0.96</v>
       </c>
-      <c r="F133" s="14" t="n">
+      <c r="F133" s="14">
         <v>0.08</v>
       </c>
       <c r="G133" s="12" t="str">
-        <f aca="false">IF(C133="idle","n/a",IF(C133=D133,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H133" s="15"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="12" t="n">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A134" s="12">
         <v>133</v>
       </c>
-      <c r="B134" s="12" t="n">
+      <c r="B134" s="12">
         <v>2</v>
       </c>
       <c r="C134" s="12" t="s">
@@ -4488,23 +4392,23 @@
       <c r="D134" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E134" s="13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F134" s="14" t="n">
+      <c r="E134" s="13">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F134" s="14">
         <v>0.08</v>
       </c>
       <c r="G134" s="12" t="str">
-        <f aca="false">IF(C134="idle","n/a",IF(C134=D134,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H134" s="15"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="12" t="n">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A135" s="12">
         <v>134</v>
       </c>
-      <c r="B135" s="12" t="n">
+      <c r="B135" s="12">
         <v>2</v>
       </c>
       <c r="C135" s="12" t="s">
@@ -4513,23 +4417,23 @@
       <c r="D135" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E135" s="13" t="n">
+      <c r="E135" s="13">
         <v>0.87</v>
       </c>
-      <c r="F135" s="14" t="n">
+      <c r="F135" s="14">
         <v>0.08</v>
       </c>
       <c r="G135" s="12" t="str">
-        <f aca="false">IF(C135="idle","n/a",IF(C135=D135,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H135" s="15"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="12" t="n">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A136" s="12">
         <v>135</v>
       </c>
-      <c r="B136" s="12" t="n">
+      <c r="B136" s="12">
         <v>2</v>
       </c>
       <c r="C136" s="12" t="s">
@@ -4538,23 +4442,23 @@
       <c r="D136" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E136" s="13" t="n">
+      <c r="E136" s="13">
         <v>0.94</v>
       </c>
-      <c r="F136" s="14" t="n">
+      <c r="F136" s="14">
         <v>0.08</v>
       </c>
       <c r="G136" s="12" t="str">
-        <f aca="false">IF(C136="idle","n/a",IF(C136=D136,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H136" s="15"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="12" t="n">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A137" s="12">
         <v>136</v>
       </c>
-      <c r="B137" s="12" t="n">
+      <c r="B137" s="12">
         <v>2</v>
       </c>
       <c r="C137" s="12" t="s">
@@ -4563,23 +4467,23 @@
       <c r="D137" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E137" s="13" t="n">
+      <c r="E137" s="13">
         <v>0.92</v>
       </c>
-      <c r="F137" s="14" t="n">
+      <c r="F137" s="14">
         <v>0.06</v>
       </c>
       <c r="G137" s="12" t="str">
-        <f aca="false">IF(C137="idle","n/a",IF(C137=D137,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H137" s="15"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="12" t="n">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A138" s="12">
         <v>137</v>
       </c>
-      <c r="B138" s="12" t="n">
+      <c r="B138" s="12">
         <v>2</v>
       </c>
       <c r="C138" s="12" t="s">
@@ -4588,23 +4492,23 @@
       <c r="D138" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E138" s="13" t="n">
+      <c r="E138" s="13">
         <v>0.87</v>
       </c>
-      <c r="F138" s="14" t="n">
-        <v>0.07</v>
+      <c r="F138" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G138" s="12" t="str">
-        <f aca="false">IF(C138="idle","n/a",IF(C138=D138,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H138" s="15"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="12" t="n">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A139" s="12">
         <v>138</v>
       </c>
-      <c r="B139" s="12" t="n">
+      <c r="B139" s="12">
         <v>2</v>
       </c>
       <c r="C139" s="12" t="s">
@@ -4613,23 +4517,23 @@
       <c r="D139" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E139" s="13" t="n">
+      <c r="E139" s="13">
         <v>0.95</v>
       </c>
-      <c r="F139" s="14" t="n">
+      <c r="F139" s="14">
         <v>0.08</v>
       </c>
       <c r="G139" s="12" t="str">
-        <f aca="false">IF(C139="idle","n/a",IF(C139=D139,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H139" s="15"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="12" t="n">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A140" s="12">
         <v>139</v>
       </c>
-      <c r="B140" s="12" t="n">
+      <c r="B140" s="12">
         <v>2</v>
       </c>
       <c r="C140" s="12" t="s">
@@ -4638,23 +4542,23 @@
       <c r="D140" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E140" s="13" t="n">
+      <c r="E140" s="13">
         <v>0.54</v>
       </c>
-      <c r="F140" s="14" t="n">
-        <v>0.07</v>
+      <c r="F140" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G140" s="12" t="str">
-        <f aca="false">IF(C140="idle","n/a",IF(C140=D140,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H140" s="15"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="12" t="n">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A141" s="12">
         <v>140</v>
       </c>
-      <c r="B141" s="12" t="n">
+      <c r="B141" s="12">
         <v>2</v>
       </c>
       <c r="C141" s="12" t="s">
@@ -4663,23 +4567,23 @@
       <c r="D141" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E141" s="13" t="n">
+      <c r="E141" s="13">
         <v>0.84</v>
       </c>
-      <c r="F141" s="14" t="n">
+      <c r="F141" s="14">
         <v>0.06</v>
       </c>
       <c r="G141" s="12" t="str">
-        <f aca="false">IF(C141="idle","n/a",IF(C141=D141,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H141" s="15"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="12" t="n">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A142" s="12">
         <v>141</v>
       </c>
-      <c r="B142" s="12" t="n">
+      <c r="B142" s="12">
         <v>2</v>
       </c>
       <c r="C142" s="12" t="s">
@@ -4688,23 +4592,23 @@
       <c r="D142" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E142" s="13" t="n">
+      <c r="E142" s="13">
         <v>0.63</v>
       </c>
-      <c r="F142" s="14" t="n">
-        <v>0.07</v>
+      <c r="F142" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G142" s="12" t="str">
-        <f aca="false">IF(C142="idle","n/a",IF(C142=D142,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H142" s="15"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="12" t="n">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A143" s="12">
         <v>142</v>
       </c>
-      <c r="B143" s="12" t="n">
+      <c r="B143" s="12">
         <v>2</v>
       </c>
       <c r="C143" s="12" t="s">
@@ -4713,23 +4617,23 @@
       <c r="D143" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E143" s="13" t="n">
+      <c r="E143" s="13">
         <v>0.92</v>
       </c>
-      <c r="F143" s="14" t="n">
+      <c r="F143" s="14">
         <v>0.06</v>
       </c>
       <c r="G143" s="12" t="str">
-        <f aca="false">IF(C143="idle","n/a",IF(C143=D143,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H143" s="15"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="12" t="n">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A144" s="12">
         <v>143</v>
       </c>
-      <c r="B144" s="12" t="n">
+      <c r="B144" s="12">
         <v>2</v>
       </c>
       <c r="C144" s="12" t="s">
@@ -4738,23 +4642,23 @@
       <c r="D144" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E144" s="13" t="n">
+      <c r="E144" s="13">
         <v>0.76</v>
       </c>
-      <c r="F144" s="14" t="n">
+      <c r="F144" s="14">
         <v>0.06</v>
       </c>
       <c r="G144" s="12" t="str">
-        <f aca="false">IF(C144="idle","n/a",IF(C144=D144,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H144" s="15"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="12" t="n">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A145" s="12">
         <v>144</v>
       </c>
-      <c r="B145" s="12" t="n">
+      <c r="B145" s="12">
         <v>2</v>
       </c>
       <c r="C145" s="12" t="s">
@@ -4763,23 +4667,23 @@
       <c r="D145" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E145" s="13" t="n">
+      <c r="E145" s="13">
         <v>0.75</v>
       </c>
-      <c r="F145" s="14" t="n">
+      <c r="F145" s="14">
         <v>0.05</v>
       </c>
       <c r="G145" s="12" t="str">
-        <f aca="false">IF(C145="idle","n/a",IF(C145=D145,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H145" s="15"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="12" t="n">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A146" s="12">
         <v>145</v>
       </c>
-      <c r="B146" s="12" t="n">
+      <c r="B146" s="12">
         <v>2</v>
       </c>
       <c r="C146" s="12" t="s">
@@ -4788,23 +4692,23 @@
       <c r="D146" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E146" s="13" t="n">
+      <c r="E146" s="13">
         <v>0.7</v>
       </c>
-      <c r="F146" s="14" t="n">
+      <c r="F146" s="14">
         <v>0.06</v>
       </c>
       <c r="G146" s="12" t="str">
-        <f aca="false">IF(C146="idle","n/a",IF(C146=D146,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H146" s="15"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="12" t="n">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A147" s="12">
         <v>146</v>
       </c>
-      <c r="B147" s="12" t="n">
+      <c r="B147" s="12">
         <v>2</v>
       </c>
       <c r="C147" s="12" t="s">
@@ -4813,23 +4717,23 @@
       <c r="D147" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E147" s="13" t="n">
+      <c r="E147" s="13">
         <v>0.73</v>
       </c>
-      <c r="F147" s="14" t="n">
+      <c r="F147" s="14">
         <v>0.04</v>
       </c>
       <c r="G147" s="12" t="str">
-        <f aca="false">IF(C147="idle","n/a",IF(C147=D147,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H147" s="15"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="12" t="n">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A148" s="12">
         <v>147</v>
       </c>
-      <c r="B148" s="12" t="n">
+      <c r="B148" s="12">
         <v>2</v>
       </c>
       <c r="C148" s="12" t="s">
@@ -4838,23 +4742,23 @@
       <c r="D148" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E148" s="13" t="n">
+      <c r="E148" s="13">
         <v>0.95</v>
       </c>
-      <c r="F148" s="14" t="n">
+      <c r="F148" s="14">
         <v>0.09</v>
       </c>
       <c r="G148" s="12" t="str">
-        <f aca="false">IF(C148="idle","n/a",IF(C148=D148,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H148" s="15"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="12" t="n">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A149" s="12">
         <v>148</v>
       </c>
-      <c r="B149" s="12" t="n">
+      <c r="B149" s="12">
         <v>2</v>
       </c>
       <c r="C149" s="12" t="s">
@@ -4863,23 +4767,23 @@
       <c r="D149" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E149" s="13" t="n">
+      <c r="E149" s="13">
         <v>0.81</v>
       </c>
-      <c r="F149" s="14" t="n">
+      <c r="F149" s="14">
         <v>0.05</v>
       </c>
       <c r="G149" s="12" t="str">
-        <f aca="false">IF(C149="idle","n/a",IF(C149=D149,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H149" s="15"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="12" t="n">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A150" s="12">
         <v>149</v>
       </c>
-      <c r="B150" s="12" t="n">
+      <c r="B150" s="12">
         <v>2</v>
       </c>
       <c r="C150" s="12" t="s">
@@ -4888,23 +4792,23 @@
       <c r="D150" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E150" s="13" t="n">
+      <c r="E150" s="13">
         <v>0.93</v>
       </c>
-      <c r="F150" s="14" t="n">
+      <c r="F150" s="14">
         <v>0.1</v>
       </c>
       <c r="G150" s="12" t="str">
-        <f aca="false">IF(C150="idle","n/a",IF(C150=D150,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H150" s="15"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="12" t="n">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A151" s="12">
         <v>150</v>
       </c>
-      <c r="B151" s="12" t="n">
+      <c r="B151" s="12">
         <v>2</v>
       </c>
       <c r="C151" s="12" t="s">
@@ -4913,23 +4817,23 @@
       <c r="D151" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E151" s="13" t="n">
+      <c r="E151" s="13">
         <v>0.48</v>
       </c>
-      <c r="F151" s="14" t="n">
+      <c r="F151" s="14">
         <v>0.05</v>
       </c>
       <c r="G151" s="12" t="str">
-        <f aca="false">IF(C151="idle","n/a",IF(C151=D151,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>No</v>
       </c>
       <c r="H151" s="15"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="12" t="n">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A152" s="12">
         <v>151</v>
       </c>
-      <c r="B152" s="12" t="n">
+      <c r="B152" s="12">
         <v>2</v>
       </c>
       <c r="C152" s="12" t="s">
@@ -4938,23 +4842,23 @@
       <c r="D152" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E152" s="13" t="n">
+      <c r="E152" s="13">
         <v>0.8</v>
       </c>
-      <c r="F152" s="14" t="n">
+      <c r="F152" s="14">
         <v>0.08</v>
       </c>
       <c r="G152" s="12" t="str">
-        <f aca="false">IF(C152="idle","n/a",IF(C152=D152,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H152" s="15"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="12" t="n">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A153" s="12">
         <v>152</v>
       </c>
-      <c r="B153" s="12" t="n">
+      <c r="B153" s="12">
         <v>2</v>
       </c>
       <c r="C153" s="12" t="s">
@@ -4963,23 +4867,23 @@
       <c r="D153" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E153" s="13" t="n">
+      <c r="E153" s="13">
         <v>0.8</v>
       </c>
-      <c r="F153" s="14" t="n">
+      <c r="F153" s="14">
         <v>0.08</v>
       </c>
       <c r="G153" s="12" t="str">
-        <f aca="false">IF(C153="idle","n/a",IF(C153=D153,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H153" s="15"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="12" t="n">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A154" s="12">
         <v>153</v>
       </c>
-      <c r="B154" s="12" t="n">
+      <c r="B154" s="12">
         <v>2</v>
       </c>
       <c r="C154" s="12" t="s">
@@ -4988,23 +4892,23 @@
       <c r="D154" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E154" s="13" t="n">
+      <c r="E154" s="13">
         <v>0.79</v>
       </c>
-      <c r="F154" s="14" t="n">
+      <c r="F154" s="14">
         <v>0.05</v>
       </c>
       <c r="G154" s="12" t="str">
-        <f aca="false">IF(C154="idle","n/a",IF(C154=D154,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H154" s="15"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="12" t="n">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A155" s="12">
         <v>154</v>
       </c>
-      <c r="B155" s="12" t="n">
+      <c r="B155" s="12">
         <v>2</v>
       </c>
       <c r="C155" s="12" t="s">
@@ -5013,23 +4917,23 @@
       <c r="D155" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E155" s="13" t="n">
+      <c r="E155" s="13">
         <v>0.92</v>
       </c>
-      <c r="F155" s="14" t="n">
+      <c r="F155" s="14">
         <v>0.06</v>
       </c>
       <c r="G155" s="12" t="str">
-        <f aca="false">IF(C155="idle","n/a",IF(C155=D155,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H155" s="15"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="12" t="n">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A156" s="12">
         <v>155</v>
       </c>
-      <c r="B156" s="12" t="n">
+      <c r="B156" s="12">
         <v>2</v>
       </c>
       <c r="C156" s="12" t="s">
@@ -5038,23 +4942,23 @@
       <c r="D156" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E156" s="13" t="n">
+      <c r="E156" s="13">
         <v>0.78</v>
       </c>
-      <c r="F156" s="14" t="n">
+      <c r="F156" s="14">
         <v>0.05</v>
       </c>
       <c r="G156" s="12" t="str">
-        <f aca="false">IF(C156="idle","n/a",IF(C156=D156,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H156" s="15"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="12" t="n">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A157" s="12">
         <v>156</v>
       </c>
-      <c r="B157" s="12" t="n">
+      <c r="B157" s="12">
         <v>2</v>
       </c>
       <c r="C157" s="12" t="s">
@@ -5063,23 +4967,23 @@
       <c r="D157" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E157" s="13" t="n">
+      <c r="E157" s="13">
         <v>0.53</v>
       </c>
-      <c r="F157" s="14" t="n">
+      <c r="F157" s="14">
         <v>0.06</v>
       </c>
       <c r="G157" s="12" t="str">
-        <f aca="false">IF(C157="idle","n/a",IF(C157=D157,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H157" s="15"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="12" t="n">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A158" s="12">
         <v>157</v>
       </c>
-      <c r="B158" s="12" t="n">
+      <c r="B158" s="12">
         <v>2</v>
       </c>
       <c r="C158" s="12" t="s">
@@ -5088,23 +4992,23 @@
       <c r="D158" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E158" s="13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F158" s="14" t="n">
+      <c r="E158" s="13">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F158" s="14">
         <v>0.04</v>
       </c>
       <c r="G158" s="12" t="str">
-        <f aca="false">IF(C158="idle","n/a",IF(C158=D158,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H158" s="15"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="12" t="n">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A159" s="12">
         <v>158</v>
       </c>
-      <c r="B159" s="12" t="n">
+      <c r="B159" s="12">
         <v>2</v>
       </c>
       <c r="C159" s="12" t="s">
@@ -5113,23 +5017,23 @@
       <c r="D159" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E159" s="13" t="n">
+      <c r="E159" s="13">
         <v>0.44</v>
       </c>
-      <c r="F159" s="14" t="n">
-        <v>0.07</v>
+      <c r="F159" s="14">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G159" s="12" t="str">
-        <f aca="false">IF(C159="idle","n/a",IF(C159=D159,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H159" s="15"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="12" t="n">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A160" s="12">
         <v>159</v>
       </c>
-      <c r="B160" s="12" t="n">
+      <c r="B160" s="12">
         <v>2</v>
       </c>
       <c r="C160" s="12" t="s">
@@ -5138,23 +5042,23 @@
       <c r="D160" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E160" s="13" t="n">
+      <c r="E160" s="13">
         <v>0.53</v>
       </c>
-      <c r="F160" s="14" t="n">
+      <c r="F160" s="14">
         <v>0.04</v>
       </c>
       <c r="G160" s="12" t="str">
-        <f aca="false">IF(C160="idle","n/a",IF(C160=D160,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H160" s="15"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="12" t="n">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A161" s="12">
         <v>160</v>
       </c>
-      <c r="B161" s="12" t="n">
+      <c r="B161" s="12">
         <v>2</v>
       </c>
       <c r="C161" s="12" t="s">
@@ -5163,23 +5067,23 @@
       <c r="D161" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E161" s="13" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="F161" s="14" t="n">
+      <c r="E161" s="13">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F161" s="14">
         <v>0.03</v>
       </c>
       <c r="G161" s="12" t="str">
-        <f aca="false">IF(C161="idle","n/a",IF(C161=D161,"Yes","No"))</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="H161" s="15"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="12" t="n">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A162" s="12">
         <v>161</v>
       </c>
-      <c r="B162" s="12" t="n">
+      <c r="B162" s="12">
         <v>2</v>
       </c>
       <c r="C162" s="12" t="s">
@@ -5188,23 +5092,23 @@
       <c r="D162" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E162" s="13" t="n">
+      <c r="E162" s="13">
         <v>0.54</v>
       </c>
-      <c r="F162" s="14" t="n">
+      <c r="F162" s="14">
         <v>0.03</v>
       </c>
       <c r="G162" s="12" t="str">
-        <f aca="false">IF(C162="idle","n/a",IF(C162=D162,"Yes","No"))</f>
+        <f t="shared" ref="G162:G170" si="5">IF(C162="idle","n/a",IF(C162=D162,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="H162" s="15"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="12" t="n">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A163" s="12">
         <v>162</v>
       </c>
-      <c r="B163" s="12" t="n">
+      <c r="B163" s="12">
         <v>2</v>
       </c>
       <c r="C163" s="12" t="s">
@@ -5213,23 +5117,23 @@
       <c r="D163" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E163" s="13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F163" s="14" t="n">
+      <c r="E163" s="13">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F163" s="14">
         <v>0.04</v>
       </c>
       <c r="G163" s="12" t="str">
-        <f aca="false">IF(C163="idle","n/a",IF(C163=D163,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H163" s="15"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="12" t="n">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A164" s="12">
         <v>163</v>
       </c>
-      <c r="B164" s="12" t="n">
+      <c r="B164" s="12">
         <v>2</v>
       </c>
       <c r="C164" s="12" t="s">
@@ -5238,23 +5142,23 @@
       <c r="D164" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E164" s="13" t="n">
+      <c r="E164" s="13">
         <v>0.39</v>
       </c>
-      <c r="F164" s="14" t="n">
+      <c r="F164" s="14">
         <v>0.04</v>
       </c>
       <c r="G164" s="12" t="str">
-        <f aca="false">IF(C164="idle","n/a",IF(C164=D164,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H164" s="15"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="12" t="n">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A165" s="12">
         <v>164</v>
       </c>
-      <c r="B165" s="12" t="n">
+      <c r="B165" s="12">
         <v>2</v>
       </c>
       <c r="C165" s="12" t="s">
@@ -5263,23 +5167,23 @@
       <c r="D165" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E165" s="13" t="n">
+      <c r="E165" s="13">
         <v>0.53</v>
       </c>
-      <c r="F165" s="14" t="n">
+      <c r="F165" s="14">
         <v>0.04</v>
       </c>
       <c r="G165" s="12" t="str">
-        <f aca="false">IF(C165="idle","n/a",IF(C165=D165,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H165" s="15"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="12" t="n">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A166" s="12">
         <v>165</v>
       </c>
-      <c r="B166" s="12" t="n">
+      <c r="B166" s="12">
         <v>2</v>
       </c>
       <c r="C166" s="12" t="s">
@@ -5288,23 +5192,23 @@
       <c r="D166" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E166" s="13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F166" s="14" t="n">
+      <c r="E166" s="13">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F166" s="14">
         <v>0.03</v>
       </c>
       <c r="G166" s="12" t="str">
-        <f aca="false">IF(C166="idle","n/a",IF(C166=D166,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H166" s="15"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="12" t="n">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A167" s="12">
         <v>166</v>
       </c>
-      <c r="B167" s="12" t="n">
+      <c r="B167" s="12">
         <v>2</v>
       </c>
       <c r="C167" s="12" t="s">
@@ -5313,23 +5217,23 @@
       <c r="D167" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E167" s="13" t="n">
+      <c r="E167" s="13">
         <v>0.88</v>
       </c>
-      <c r="F167" s="14" t="n">
+      <c r="F167" s="14">
         <v>0.04</v>
       </c>
       <c r="G167" s="12" t="str">
-        <f aca="false">IF(C167="idle","n/a",IF(C167=D167,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H167" s="15"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="12" t="n">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A168" s="12">
         <v>167</v>
       </c>
-      <c r="B168" s="12" t="n">
+      <c r="B168" s="12">
         <v>2</v>
       </c>
       <c r="C168" s="12" t="s">
@@ -5338,23 +5242,23 @@
       <c r="D168" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E168" s="13" t="n">
+      <c r="E168" s="13">
         <v>0.85</v>
       </c>
-      <c r="F168" s="14" t="n">
+      <c r="F168" s="14">
         <v>0.04</v>
       </c>
       <c r="G168" s="12" t="str">
-        <f aca="false">IF(C168="idle","n/a",IF(C168=D168,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H168" s="15"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="12" t="n">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A169" s="12">
         <v>168</v>
       </c>
-      <c r="B169" s="12" t="n">
+      <c r="B169" s="12">
         <v>2</v>
       </c>
       <c r="C169" s="12" t="s">
@@ -5363,23 +5267,23 @@
       <c r="D169" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E169" s="13" t="n">
+      <c r="E169" s="13">
         <v>0.6</v>
       </c>
-      <c r="F169" s="14" t="n">
+      <c r="F169" s="14">
         <v>0.04</v>
       </c>
       <c r="G169" s="12" t="str">
-        <f aca="false">IF(C169="idle","n/a",IF(C169=D169,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H169" s="15"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="12" t="n">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A170" s="12">
         <v>169</v>
       </c>
-      <c r="B170" s="12" t="n">
+      <c r="B170" s="12">
         <v>2</v>
       </c>
       <c r="C170" s="12" t="s">
@@ -5388,40 +5292,34 @@
       <c r="D170" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E170" s="13" t="n">
+      <c r="E170" s="13">
         <v>0.71</v>
       </c>
-      <c r="F170" s="14" t="n">
+      <c r="F170" s="14">
         <v>0.04</v>
       </c>
       <c r="G170" s="12" t="str">
-        <f aca="false">IF(C170="idle","n/a",IF(C170=D170,"Yes","No"))</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="H170" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H170"/>
+  <autoFilter ref="A1:H170" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="E2:E170">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
+      <formula>0.6</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G170">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E170">
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0.6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>